--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mat/Library/Mobile Documents/com~apple~CloudDocs/_ETML/Modules/ICT-293/Projet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697E3415-B233-7B41-9298-AC1EAF26780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E45D77-D6F4-4BB0-BFBA-5B261372BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="33600" windowHeight="18160" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>Auteur:</t>
   </si>
@@ -130,10 +130,13 @@
     <t>Journal de travail</t>
   </si>
   <si>
-    <t>P_WebStatique 293</t>
+    <t>Création des maquettes</t>
   </si>
   <si>
-    <t>24.02.2025 au 14.03.2025</t>
+    <t>Visuel du site</t>
+  </si>
+  <si>
+    <t>P_AppMobile</t>
   </si>
 </sst>
 </file>
@@ -851,7 +854,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -888,7 +891,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-CH"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1017,7 +1020,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-CH"/>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="ctr"/>
@@ -1076,7 +1079,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1140,7 +1143,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-CH"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1177,7 +1180,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-CH"/>
+      <a:endParaRPr lang="fr-FR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1191,7 +1194,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1228,7 +1231,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-CH"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1364,7 +1367,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-CH"/>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="ctr"/>
@@ -1487,7 +1490,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-CH"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1524,7 +1527,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-CH"/>
+      <a:endParaRPr lang="fr-FR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1538,7 +1541,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1606,7 +1609,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-CH"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1763,7 +1766,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-CH"/>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1881,7 +1884,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-CH"/>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1928,7 +1931,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1999,7 +2002,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-CH"/>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="686342815"/>
@@ -2083,7 +2086,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-CH"/>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2120,7 +2123,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-CH"/>
+      <a:endParaRPr lang="fr-FR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4117,24 +4120,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF2E8F1-C793-7E43-B3DE-C075053A97DA}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O532"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="83.5" customWidth="1"/>
-    <col min="7" max="7" width="72.1640625" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.125" customWidth="1"/>
+    <col min="10" max="10" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="7.5" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="11" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
       <c r="B1" s="9"/>
       <c r="C1" s="10"/>
@@ -4145,7 +4148,7 @@
       </c>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="82" t="s">
         <v>0</v>
       </c>
@@ -4159,51 +4162,49 @@
         <v>1</v>
       </c>
       <c r="G2" s="75" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="82" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>0 heures 0 minutes</v>
+        <v>3 heures 45 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
       <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="76" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="76"/>
+    </row>
+    <row r="4" spans="1:15" ht="23.25" hidden="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C5" s="81" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="81"/>
     </row>
-    <row r="6" spans="1:15" s="17" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="17" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
@@ -4226,28 +4227,48 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="72" t="str">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="72">
         <f>IF(ISBLANK(B7),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B7))</f>
-        <v/>
-      </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="28"/>
+        <v>12</v>
+      </c>
+      <c r="B7" s="32">
+        <v>46099</v>
+      </c>
+      <c r="C7" s="33">
+        <v>2</v>
+      </c>
+      <c r="D7" s="34">
+        <v>15</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>29</v>
+      </c>
       <c r="G7" s="44"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="73" t="str">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="73">
         <f>IF(ISBLANK(B8),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B8))</f>
-        <v/>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="28"/>
+        <v>13</v>
+      </c>
+      <c r="B8" s="36">
+        <v>46106</v>
+      </c>
+      <c r="C8" s="37">
+        <v>1</v>
+      </c>
+      <c r="D8" s="38">
+        <v>30</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>30</v>
+      </c>
       <c r="G8" s="45"/>
       <c r="M8" t="s">
         <v>2</v>
@@ -4259,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="str">
         <f>IF(ISBLANK(B9),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B9))</f>
         <v/>
@@ -4280,7 +4301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="73" t="str">
         <f>IF(ISBLANK(B10),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B10))</f>
         <v/>
@@ -4301,7 +4322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="str">
         <f>IF(ISBLANK(B11),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B11))</f>
         <v/>
@@ -4322,7 +4343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="73" t="str">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
         <v/>
@@ -4340,7 +4361,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="74" t="str">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
         <v/>
@@ -4358,7 +4379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="73" t="str">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
         <v/>
@@ -4376,7 +4397,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="74" t="str">
         <f>IF(ISBLANK(B15),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B15))</f>
         <v/>
@@ -4394,7 +4415,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="str">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
         <v/>
@@ -4409,7 +4430,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="str">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
         <v/>
@@ -4424,7 +4445,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="73" t="str">
         <f>IF(ISBLANK(B18),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B18))</f>
         <v/>
@@ -4439,7 +4460,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="74" t="str">
         <f>IF(ISBLANK(B19),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B19))</f>
         <v/>
@@ -4454,7 +4475,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="73" t="str">
         <f>IF(ISBLANK(B20),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B20))</f>
         <v/>
@@ -4466,7 +4487,7 @@
       <c r="F20" s="28"/>
       <c r="G20" s="45"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="74" t="str">
         <f>IF(ISBLANK(B21),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B21))</f>
         <v/>
@@ -4478,7 +4499,7 @@
       <c r="F21" s="28"/>
       <c r="G21" s="46"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="73" t="str">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
         <v/>
@@ -4490,7 +4511,7 @@
       <c r="F22" s="28"/>
       <c r="G22" s="45"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="74" t="str">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
         <v/>
@@ -4502,7 +4523,7 @@
       <c r="F23" s="28"/>
       <c r="G23" s="46"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="73" t="str">
         <f>IF(ISBLANK(B24),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B24))</f>
         <v/>
@@ -4514,7 +4535,7 @@
       <c r="F24" s="28"/>
       <c r="G24" s="45"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="74" t="str">
         <f>IF(ISBLANK(B25),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B25))</f>
         <v/>
@@ -4526,7 +4547,7 @@
       <c r="F25" s="28"/>
       <c r="G25" s="46"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="73" t="str">
         <f>IF(ISBLANK(B26),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B26))</f>
         <v/>
@@ -4538,7 +4559,7 @@
       <c r="F26" s="28"/>
       <c r="G26" s="45"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="74" t="str">
         <f>IF(ISBLANK(B27),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B27))</f>
         <v/>
@@ -4550,7 +4571,7 @@
       <c r="F27" s="28"/>
       <c r="G27" s="46"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="73" t="str">
         <f>IF(ISBLANK(B28),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B28))</f>
         <v/>
@@ -4562,7 +4583,7 @@
       <c r="F28" s="27"/>
       <c r="G28" s="45"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="74" t="str">
         <f>IF(ISBLANK(B29),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B29))</f>
         <v/>
@@ -4574,7 +4595,7 @@
       <c r="F29" s="27"/>
       <c r="G29" s="46"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="73" t="str">
         <f>IF(ISBLANK(B30),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B30))</f>
         <v/>
@@ -4586,7 +4607,7 @@
       <c r="F30" s="28"/>
       <c r="G30" s="45"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="74" t="str">
         <f>IF(ISBLANK(B31),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B31))</f>
         <v/>
@@ -4598,7 +4619,7 @@
       <c r="F31" s="27"/>
       <c r="G31" s="46"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="73" t="str">
         <f>IF(ISBLANK(B32),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B32))</f>
         <v/>
@@ -4610,7 +4631,7 @@
       <c r="F32" s="28"/>
       <c r="G32" s="45"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="74" t="str">
         <f>IF(ISBLANK(B33),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B33))</f>
         <v/>
@@ -4622,7 +4643,7 @@
       <c r="F33" s="27"/>
       <c r="G33" s="46"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="73" t="str">
         <f>IF(ISBLANK(B34),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B34))</f>
         <v/>
@@ -4634,7 +4655,7 @@
       <c r="F34" s="27"/>
       <c r="G34" s="45"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="74" t="str">
         <f>IF(ISBLANK(B35),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B35))</f>
         <v/>
@@ -4646,7 +4667,7 @@
       <c r="F35" s="28"/>
       <c r="G35" s="46"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="73" t="str">
         <f>IF(ISBLANK(B36),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B36))</f>
         <v/>
@@ -4658,7 +4679,7 @@
       <c r="F36" s="27"/>
       <c r="G36" s="45"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="74" t="str">
         <f>IF(ISBLANK(B37),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B37))</f>
         <v/>
@@ -4670,7 +4691,7 @@
       <c r="F37" s="27"/>
       <c r="G37" s="46"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="73" t="str">
         <f>IF(ISBLANK(B38),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B38))</f>
         <v/>
@@ -4682,7 +4703,7 @@
       <c r="F38" s="27"/>
       <c r="G38" s="45"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="74" t="str">
         <f>IF(ISBLANK(B39),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B39))</f>
         <v/>
@@ -4694,7 +4715,7 @@
       <c r="F39" s="27"/>
       <c r="G39" s="46"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="73" t="str">
         <f>IF(ISBLANK(B40),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B40))</f>
         <v/>
@@ -4706,7 +4727,7 @@
       <c r="F40" s="27"/>
       <c r="G40" s="45"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="74" t="str">
         <f>IF(ISBLANK(B41),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B41))</f>
         <v/>
@@ -4718,7 +4739,7 @@
       <c r="F41" s="27"/>
       <c r="G41" s="46"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="73" t="str">
         <f>IF(ISBLANK(B42),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B42))</f>
         <v/>
@@ -4730,7 +4751,7 @@
       <c r="F42" s="27"/>
       <c r="G42" s="45"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="74" t="str">
         <f>IF(ISBLANK(B43),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B43))</f>
         <v/>
@@ -4742,7 +4763,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="46"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="73" t="str">
         <f>IF(ISBLANK(B44),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B44))</f>
         <v/>
@@ -4754,7 +4775,7 @@
       <c r="F44" s="27"/>
       <c r="G44" s="45"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="74" t="str">
         <f>IF(ISBLANK(B45),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B45))</f>
         <v/>
@@ -4766,7 +4787,7 @@
       <c r="F45" s="27"/>
       <c r="G45" s="46"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="73" t="str">
         <f>IF(ISBLANK(B46),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B46))</f>
         <v/>
@@ -4778,7 +4799,7 @@
       <c r="F46" s="27"/>
       <c r="G46" s="45"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="74" t="str">
         <f>IF(ISBLANK(B47),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B47))</f>
         <v/>
@@ -4790,7 +4811,7 @@
       <c r="F47" s="27"/>
       <c r="G47" s="46"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="73" t="str">
         <f>IF(ISBLANK(B48),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B48))</f>
         <v/>
@@ -4802,7 +4823,7 @@
       <c r="F48" s="27"/>
       <c r="G48" s="45"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="74" t="str">
         <f>IF(ISBLANK(B49),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B49))</f>
         <v/>
@@ -4814,7 +4835,7 @@
       <c r="F49" s="27"/>
       <c r="G49" s="46"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="73" t="str">
         <f>IF(ISBLANK(B50),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B50))</f>
         <v/>
@@ -4826,7 +4847,7 @@
       <c r="F50" s="27"/>
       <c r="G50" s="45"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="74" t="str">
         <f>IF(ISBLANK(B51),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B51))</f>
         <v/>
@@ -4838,7 +4859,7 @@
       <c r="F51" s="27"/>
       <c r="G51" s="46"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="73" t="str">
         <f>IF(ISBLANK(B52),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B52))</f>
         <v/>
@@ -4850,7 +4871,7 @@
       <c r="F52" s="27"/>
       <c r="G52" s="45"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="74" t="str">
         <f>IF(ISBLANK(B53),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B53))</f>
         <v/>
@@ -4862,7 +4883,7 @@
       <c r="F53" s="27"/>
       <c r="G53" s="46"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="73" t="str">
         <f>IF(ISBLANK(B54),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B54))</f>
         <v/>
@@ -4874,7 +4895,7 @@
       <c r="F54" s="27"/>
       <c r="G54" s="45"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="74" t="str">
         <f>IF(ISBLANK(B55),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B55))</f>
         <v/>
@@ -4886,7 +4907,7 @@
       <c r="F55" s="27"/>
       <c r="G55" s="46"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="73" t="str">
         <f>IF(ISBLANK(B56),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B56))</f>
         <v/>
@@ -4898,7 +4919,7 @@
       <c r="F56" s="13"/>
       <c r="G56" s="45"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="74" t="str">
         <f>IF(ISBLANK(B57),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B57))</f>
         <v/>
@@ -4910,7 +4931,7 @@
       <c r="F57" s="14"/>
       <c r="G57" s="46"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="73" t="str">
         <f>IF(ISBLANK(B58),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B58))</f>
         <v/>
@@ -4922,7 +4943,7 @@
       <c r="F58" s="13"/>
       <c r="G58" s="45"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="74" t="str">
         <f>IF(ISBLANK(B59),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B59))</f>
         <v/>
@@ -4934,7 +4955,7 @@
       <c r="F59" s="14"/>
       <c r="G59" s="46"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="73" t="str">
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v/>
@@ -4946,7 +4967,7 @@
       <c r="F60" s="13"/>
       <c r="G60" s="45"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="74" t="str">
         <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
         <v/>
@@ -4958,7 +4979,7 @@
       <c r="F61" s="14"/>
       <c r="G61" s="46"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="73" t="str">
         <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
         <v/>
@@ -4970,7 +4991,7 @@
       <c r="F62" s="13"/>
       <c r="G62" s="45"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="74" t="str">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
         <v/>
@@ -4982,7 +5003,7 @@
       <c r="F63" s="14"/>
       <c r="G63" s="46"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="73" t="str">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
         <v/>
@@ -4994,7 +5015,7 @@
       <c r="F64" s="13"/>
       <c r="G64" s="45"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="74" t="str">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
         <v/>
@@ -5006,7 +5027,7 @@
       <c r="F65" s="14"/>
       <c r="G65" s="46"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="73" t="str">
         <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
         <v/>
@@ -5018,7 +5039,7 @@
       <c r="F66" s="13"/>
       <c r="G66" s="45"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="74" t="str">
         <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
         <v/>
@@ -5030,7 +5051,7 @@
       <c r="F67" s="14"/>
       <c r="G67" s="46"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="73" t="str">
         <f>IF(ISBLANK(B68),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B68))</f>
         <v/>
@@ -5042,7 +5063,7 @@
       <c r="F68" s="13"/>
       <c r="G68" s="45"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="74" t="str">
         <f>IF(ISBLANK(B69),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B69))</f>
         <v/>
@@ -5054,7 +5075,7 @@
       <c r="F69" s="14"/>
       <c r="G69" s="46"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="73" t="str">
         <f>IF(ISBLANK(B70),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B70))</f>
         <v/>
@@ -5066,7 +5087,7 @@
       <c r="F70" s="13"/>
       <c r="G70" s="45"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="74" t="str">
         <f>IF(ISBLANK(B71),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B71))</f>
         <v/>
@@ -5078,7 +5099,7 @@
       <c r="F71" s="14"/>
       <c r="G71" s="46"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="73" t="str">
         <f>IF(ISBLANK(B72),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B72))</f>
         <v/>
@@ -5090,7 +5111,7 @@
       <c r="F72" s="13"/>
       <c r="G72" s="45"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="74" t="str">
         <f>IF(ISBLANK(B73),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B73))</f>
         <v/>
@@ -5102,7 +5123,7 @@
       <c r="F73" s="14"/>
       <c r="G73" s="46"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="73" t="str">
         <f>IF(ISBLANK(B74),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B74))</f>
         <v/>
@@ -5114,7 +5135,7 @@
       <c r="F74" s="13"/>
       <c r="G74" s="45"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="74" t="str">
         <f>IF(ISBLANK(B75),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B75))</f>
         <v/>
@@ -5126,7 +5147,7 @@
       <c r="F75" s="14"/>
       <c r="G75" s="46"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="73" t="str">
         <f>IF(ISBLANK(B76),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B76))</f>
         <v/>
@@ -5138,7 +5159,7 @@
       <c r="F76" s="13"/>
       <c r="G76" s="45"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="74" t="str">
         <f>IF(ISBLANK(B77),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B77))</f>
         <v/>
@@ -5150,7 +5171,7 @@
       <c r="F77" s="14"/>
       <c r="G77" s="46"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="73" t="str">
         <f>IF(ISBLANK(B78),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B78))</f>
         <v/>
@@ -5162,7 +5183,7 @@
       <c r="F78" s="13"/>
       <c r="G78" s="45"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="74" t="str">
         <f>IF(ISBLANK(B79),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B79))</f>
         <v/>
@@ -5174,7 +5195,7 @@
       <c r="F79" s="14"/>
       <c r="G79" s="46"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="73" t="str">
         <f>IF(ISBLANK(B80),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B80))</f>
         <v/>
@@ -5186,7 +5207,7 @@
       <c r="F80" s="13"/>
       <c r="G80" s="45"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="74" t="str">
         <f>IF(ISBLANK(B81),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B81))</f>
         <v/>
@@ -5198,7 +5219,7 @@
       <c r="F81" s="14"/>
       <c r="G81" s="46"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="73" t="str">
         <f>IF(ISBLANK(B82),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B82))</f>
         <v/>
@@ -5210,7 +5231,7 @@
       <c r="F82" s="13"/>
       <c r="G82" s="45"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="74" t="str">
         <f>IF(ISBLANK(B83),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B83))</f>
         <v/>
@@ -5222,7 +5243,7 @@
       <c r="F83" s="14"/>
       <c r="G83" s="46"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="73" t="str">
         <f>IF(ISBLANK(B84),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B84))</f>
         <v/>
@@ -5234,7 +5255,7 @@
       <c r="F84" s="13"/>
       <c r="G84" s="45"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="74" t="str">
         <f>IF(ISBLANK(B85),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B85))</f>
         <v/>
@@ -5246,7 +5267,7 @@
       <c r="F85" s="14"/>
       <c r="G85" s="46"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="73" t="str">
         <f>IF(ISBLANK(B86),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B86))</f>
         <v/>
@@ -5258,7 +5279,7 @@
       <c r="F86" s="13"/>
       <c r="G86" s="45"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="74" t="str">
         <f>IF(ISBLANK(B87),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B87))</f>
         <v/>
@@ -5270,7 +5291,7 @@
       <c r="F87" s="14"/>
       <c r="G87" s="46"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="73" t="str">
         <f>IF(ISBLANK(B88),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B88))</f>
         <v/>
@@ -5282,7 +5303,7 @@
       <c r="F88" s="13"/>
       <c r="G88" s="45"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="74" t="str">
         <f>IF(ISBLANK(B89),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B89))</f>
         <v/>
@@ -5294,7 +5315,7 @@
       <c r="F89" s="14"/>
       <c r="G89" s="46"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="73" t="str">
         <f>IF(ISBLANK(B90),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B90))</f>
         <v/>
@@ -5306,7 +5327,7 @@
       <c r="F90" s="13"/>
       <c r="G90" s="45"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="74" t="str">
         <f>IF(ISBLANK(B91),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B91))</f>
         <v/>
@@ -5318,7 +5339,7 @@
       <c r="F91" s="14"/>
       <c r="G91" s="46"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="73" t="str">
         <f>IF(ISBLANK(B92),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B92))</f>
         <v/>
@@ -5330,7 +5351,7 @@
       <c r="F92" s="13"/>
       <c r="G92" s="45"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="74" t="str">
         <f>IF(ISBLANK(B93),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B93))</f>
         <v/>
@@ -5342,7 +5363,7 @@
       <c r="F93" s="14"/>
       <c r="G93" s="46"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="73" t="str">
         <f>IF(ISBLANK(B94),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B94))</f>
         <v/>
@@ -5354,7 +5375,7 @@
       <c r="F94" s="13"/>
       <c r="G94" s="45"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="74" t="str">
         <f>IF(ISBLANK(B95),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B95))</f>
         <v/>
@@ -5366,7 +5387,7 @@
       <c r="F95" s="14"/>
       <c r="G95" s="46"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="73" t="str">
         <f>IF(ISBLANK(B96),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B96))</f>
         <v/>
@@ -5378,7 +5399,7 @@
       <c r="F96" s="13"/>
       <c r="G96" s="45"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="74" t="str">
         <f>IF(ISBLANK(B97),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B97))</f>
         <v/>
@@ -5390,7 +5411,7 @@
       <c r="F97" s="14"/>
       <c r="G97" s="46"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="73" t="str">
         <f>IF(ISBLANK(B98),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B98))</f>
         <v/>
@@ -5402,7 +5423,7 @@
       <c r="F98" s="13"/>
       <c r="G98" s="45"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="74" t="str">
         <f>IF(ISBLANK(B99),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B99))</f>
         <v/>
@@ -5414,7 +5435,7 @@
       <c r="F99" s="14"/>
       <c r="G99" s="46"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="73" t="str">
         <f>IF(ISBLANK(B100),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B100))</f>
         <v/>
@@ -5426,7 +5447,7 @@
       <c r="F100" s="13"/>
       <c r="G100" s="45"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="74" t="str">
         <f>IF(ISBLANK(B101),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B101))</f>
         <v/>
@@ -5438,7 +5459,7 @@
       <c r="F101" s="14"/>
       <c r="G101" s="46"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="73" t="str">
         <f>IF(ISBLANK(B102),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B102))</f>
         <v/>
@@ -5450,7 +5471,7 @@
       <c r="F102" s="13"/>
       <c r="G102" s="45"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="74" t="str">
         <f>IF(ISBLANK(B103),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B103))</f>
         <v/>
@@ -5462,7 +5483,7 @@
       <c r="F103" s="14"/>
       <c r="G103" s="46"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="73" t="str">
         <f>IF(ISBLANK(B104),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B104))</f>
         <v/>
@@ -5474,7 +5495,7 @@
       <c r="F104" s="13"/>
       <c r="G104" s="45"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="74" t="str">
         <f>IF(ISBLANK(B105),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B105))</f>
         <v/>
@@ -5486,7 +5507,7 @@
       <c r="F105" s="14"/>
       <c r="G105" s="46"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="73" t="str">
         <f>IF(ISBLANK(B106),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B106))</f>
         <v/>
@@ -5498,7 +5519,7 @@
       <c r="F106" s="13"/>
       <c r="G106" s="45"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="74" t="str">
         <f>IF(ISBLANK(B107),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B107))</f>
         <v/>
@@ -5510,7 +5531,7 @@
       <c r="F107" s="14"/>
       <c r="G107" s="46"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="73" t="str">
         <f>IF(ISBLANK(B108),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B108))</f>
         <v/>
@@ -5522,7 +5543,7 @@
       <c r="F108" s="13"/>
       <c r="G108" s="45"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="74" t="str">
         <f>IF(ISBLANK(B109),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B109))</f>
         <v/>
@@ -5534,7 +5555,7 @@
       <c r="F109" s="14"/>
       <c r="G109" s="46"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="73" t="str">
         <f>IF(ISBLANK(B110),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B110))</f>
         <v/>
@@ -5546,7 +5567,7 @@
       <c r="F110" s="13"/>
       <c r="G110" s="45"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="74" t="str">
         <f>IF(ISBLANK(B111),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B111))</f>
         <v/>
@@ -5558,7 +5579,7 @@
       <c r="F111" s="14"/>
       <c r="G111" s="46"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="73" t="str">
         <f>IF(ISBLANK(B112),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B112))</f>
         <v/>
@@ -5570,7 +5591,7 @@
       <c r="F112" s="13"/>
       <c r="G112" s="45"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="74" t="str">
         <f>IF(ISBLANK(B113),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B113))</f>
         <v/>
@@ -5582,7 +5603,7 @@
       <c r="F113" s="14"/>
       <c r="G113" s="46"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="73" t="str">
         <f>IF(ISBLANK(B114),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B114))</f>
         <v/>
@@ -5594,7 +5615,7 @@
       <c r="F114" s="13"/>
       <c r="G114" s="45"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="74" t="str">
         <f>IF(ISBLANK(B115),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B115))</f>
         <v/>
@@ -5606,7 +5627,7 @@
       <c r="F115" s="14"/>
       <c r="G115" s="46"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="73" t="str">
         <f>IF(ISBLANK(B116),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B116))</f>
         <v/>
@@ -5618,7 +5639,7 @@
       <c r="F116" s="13"/>
       <c r="G116" s="45"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="74" t="str">
         <f>IF(ISBLANK(B117),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B117))</f>
         <v/>
@@ -5630,7 +5651,7 @@
       <c r="F117" s="14"/>
       <c r="G117" s="46"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="73" t="str">
         <f>IF(ISBLANK(B118),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B118))</f>
         <v/>
@@ -5642,7 +5663,7 @@
       <c r="F118" s="13"/>
       <c r="G118" s="45"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="74" t="str">
         <f>IF(ISBLANK(B119),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B119))</f>
         <v/>
@@ -5654,7 +5675,7 @@
       <c r="F119" s="14"/>
       <c r="G119" s="46"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="73" t="str">
         <f>IF(ISBLANK(B120),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B120))</f>
         <v/>
@@ -5666,7 +5687,7 @@
       <c r="F120" s="13"/>
       <c r="G120" s="45"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="74" t="str">
         <f>IF(ISBLANK(B121),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B121))</f>
         <v/>
@@ -5678,7 +5699,7 @@
       <c r="F121" s="14"/>
       <c r="G121" s="46"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="73" t="str">
         <f>IF(ISBLANK(B122),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B122))</f>
         <v/>
@@ -5690,7 +5711,7 @@
       <c r="F122" s="13"/>
       <c r="G122" s="45"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="74" t="str">
         <f>IF(ISBLANK(B123),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B123))</f>
         <v/>
@@ -5702,7 +5723,7 @@
       <c r="F123" s="14"/>
       <c r="G123" s="46"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="73" t="str">
         <f>IF(ISBLANK(B124),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B124))</f>
         <v/>
@@ -5714,7 +5735,7 @@
       <c r="F124" s="13"/>
       <c r="G124" s="45"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="74" t="str">
         <f>IF(ISBLANK(B125),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B125))</f>
         <v/>
@@ -5726,7 +5747,7 @@
       <c r="F125" s="14"/>
       <c r="G125" s="46"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="73" t="str">
         <f>IF(ISBLANK(B126),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B126))</f>
         <v/>
@@ -5738,7 +5759,7 @@
       <c r="F126" s="13"/>
       <c r="G126" s="45"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="74" t="str">
         <f>IF(ISBLANK(B127),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B127))</f>
         <v/>
@@ -5750,7 +5771,7 @@
       <c r="F127" s="14"/>
       <c r="G127" s="46"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="73" t="str">
         <f>IF(ISBLANK(B128),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B128))</f>
         <v/>
@@ -5762,7 +5783,7 @@
       <c r="F128" s="13"/>
       <c r="G128" s="45"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="74" t="str">
         <f>IF(ISBLANK(B129),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B129))</f>
         <v/>
@@ -5774,7 +5795,7 @@
       <c r="F129" s="14"/>
       <c r="G129" s="46"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="73" t="str">
         <f>IF(ISBLANK(B130),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B130))</f>
         <v/>
@@ -5786,7 +5807,7 @@
       <c r="F130" s="13"/>
       <c r="G130" s="45"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="74" t="str">
         <f>IF(ISBLANK(B131),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B131))</f>
         <v/>
@@ -5798,7 +5819,7 @@
       <c r="F131" s="14"/>
       <c r="G131" s="46"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="73" t="str">
         <f>IF(ISBLANK(B132),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B132))</f>
         <v/>
@@ -5810,7 +5831,7 @@
       <c r="F132" s="13"/>
       <c r="G132" s="45"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="74" t="str">
         <f>IF(ISBLANK(B133),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B133))</f>
         <v/>
@@ -5822,7 +5843,7 @@
       <c r="F133" s="14"/>
       <c r="G133" s="46"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="73" t="str">
         <f>IF(ISBLANK(B134),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B134))</f>
         <v/>
@@ -5834,7 +5855,7 @@
       <c r="F134" s="13"/>
       <c r="G134" s="45"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="74" t="str">
         <f>IF(ISBLANK(B135),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B135))</f>
         <v/>
@@ -5846,7 +5867,7 @@
       <c r="F135" s="14"/>
       <c r="G135" s="46"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="73" t="str">
         <f>IF(ISBLANK(B136),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B136))</f>
         <v/>
@@ -5858,7 +5879,7 @@
       <c r="F136" s="13"/>
       <c r="G136" s="45"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="74" t="str">
         <f>IF(ISBLANK(B137),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B137))</f>
         <v/>
@@ -5870,7 +5891,7 @@
       <c r="F137" s="14"/>
       <c r="G137" s="46"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="73" t="str">
         <f>IF(ISBLANK(B138),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B138))</f>
         <v/>
@@ -5882,7 +5903,7 @@
       <c r="F138" s="13"/>
       <c r="G138" s="45"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="74" t="str">
         <f>IF(ISBLANK(B139),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B139))</f>
         <v/>
@@ -5894,7 +5915,7 @@
       <c r="F139" s="14"/>
       <c r="G139" s="46"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="73" t="str">
         <f>IF(ISBLANK(B140),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B140))</f>
         <v/>
@@ -5906,7 +5927,7 @@
       <c r="F140" s="13"/>
       <c r="G140" s="45"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="74" t="str">
         <f>IF(ISBLANK(B141),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B141))</f>
         <v/>
@@ -5918,7 +5939,7 @@
       <c r="F141" s="14"/>
       <c r="G141" s="46"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="73" t="str">
         <f>IF(ISBLANK(B142),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B142))</f>
         <v/>
@@ -5930,7 +5951,7 @@
       <c r="F142" s="13"/>
       <c r="G142" s="45"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="74" t="str">
         <f>IF(ISBLANK(B143),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B143))</f>
         <v/>
@@ -5942,7 +5963,7 @@
       <c r="F143" s="14"/>
       <c r="G143" s="46"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="73" t="str">
         <f>IF(ISBLANK(B144),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B144))</f>
         <v/>
@@ -5954,7 +5975,7 @@
       <c r="F144" s="13"/>
       <c r="G144" s="45"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="74" t="str">
         <f>IF(ISBLANK(B145),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B145))</f>
         <v/>
@@ -5966,7 +5987,7 @@
       <c r="F145" s="14"/>
       <c r="G145" s="46"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="73" t="str">
         <f>IF(ISBLANK(B146),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B146))</f>
         <v/>
@@ -5978,7 +5999,7 @@
       <c r="F146" s="13"/>
       <c r="G146" s="45"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="74" t="str">
         <f>IF(ISBLANK(B147),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B147))</f>
         <v/>
@@ -5990,7 +6011,7 @@
       <c r="F147" s="14"/>
       <c r="G147" s="46"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="73" t="str">
         <f>IF(ISBLANK(B148),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B148))</f>
         <v/>
@@ -6002,7 +6023,7 @@
       <c r="F148" s="13"/>
       <c r="G148" s="45"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="74" t="str">
         <f>IF(ISBLANK(B149),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B149))</f>
         <v/>
@@ -6014,7 +6035,7 @@
       <c r="F149" s="14"/>
       <c r="G149" s="46"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="73" t="str">
         <f>IF(ISBLANK(B150),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B150))</f>
         <v/>
@@ -6026,7 +6047,7 @@
       <c r="F150" s="13"/>
       <c r="G150" s="45"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="74" t="str">
         <f>IF(ISBLANK(B151),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B151))</f>
         <v/>
@@ -6038,7 +6059,7 @@
       <c r="F151" s="14"/>
       <c r="G151" s="46"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="73" t="str">
         <f>IF(ISBLANK(B152),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B152))</f>
         <v/>
@@ -6050,7 +6071,7 @@
       <c r="F152" s="13"/>
       <c r="G152" s="45"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="74" t="str">
         <f>IF(ISBLANK(B153),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B153))</f>
         <v/>
@@ -6062,7 +6083,7 @@
       <c r="F153" s="14"/>
       <c r="G153" s="46"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="73" t="str">
         <f>IF(ISBLANK(B154),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B154))</f>
         <v/>
@@ -6074,7 +6095,7 @@
       <c r="F154" s="13"/>
       <c r="G154" s="45"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="74" t="str">
         <f>IF(ISBLANK(B155),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B155))</f>
         <v/>
@@ -6086,7 +6107,7 @@
       <c r="F155" s="14"/>
       <c r="G155" s="46"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="73" t="str">
         <f>IF(ISBLANK(B156),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B156))</f>
         <v/>
@@ -6098,7 +6119,7 @@
       <c r="F156" s="13"/>
       <c r="G156" s="45"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="74" t="str">
         <f>IF(ISBLANK(B157),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B157))</f>
         <v/>
@@ -6110,7 +6131,7 @@
       <c r="F157" s="14"/>
       <c r="G157" s="46"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="73" t="str">
         <f>IF(ISBLANK(B158),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B158))</f>
         <v/>
@@ -6122,7 +6143,7 @@
       <c r="F158" s="13"/>
       <c r="G158" s="45"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="74" t="str">
         <f>IF(ISBLANK(B159),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B159))</f>
         <v/>
@@ -6134,7 +6155,7 @@
       <c r="F159" s="14"/>
       <c r="G159" s="46"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="73" t="str">
         <f>IF(ISBLANK(B160),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B160))</f>
         <v/>
@@ -6146,7 +6167,7 @@
       <c r="F160" s="13"/>
       <c r="G160" s="45"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="74" t="str">
         <f>IF(ISBLANK(B161),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B161))</f>
         <v/>
@@ -6158,7 +6179,7 @@
       <c r="F161" s="14"/>
       <c r="G161" s="46"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="73" t="str">
         <f>IF(ISBLANK(B162),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B162))</f>
         <v/>
@@ -6170,7 +6191,7 @@
       <c r="F162" s="13"/>
       <c r="G162" s="45"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="74" t="str">
         <f>IF(ISBLANK(B163),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B163))</f>
         <v/>
@@ -6182,7 +6203,7 @@
       <c r="F163" s="14"/>
       <c r="G163" s="46"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="73" t="str">
         <f>IF(ISBLANK(B164),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B164))</f>
         <v/>
@@ -6194,7 +6215,7 @@
       <c r="F164" s="13"/>
       <c r="G164" s="45"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="74" t="str">
         <f>IF(ISBLANK(B165),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B165))</f>
         <v/>
@@ -6206,7 +6227,7 @@
       <c r="F165" s="14"/>
       <c r="G165" s="46"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="73" t="str">
         <f>IF(ISBLANK(B166),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B166))</f>
         <v/>
@@ -6218,7 +6239,7 @@
       <c r="F166" s="13"/>
       <c r="G166" s="45"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="74" t="str">
         <f>IF(ISBLANK(B167),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B167))</f>
         <v/>
@@ -6230,7 +6251,7 @@
       <c r="F167" s="14"/>
       <c r="G167" s="46"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="73" t="str">
         <f>IF(ISBLANK(B168),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B168))</f>
         <v/>
@@ -6242,7 +6263,7 @@
       <c r="F168" s="13"/>
       <c r="G168" s="45"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="74" t="str">
         <f>IF(ISBLANK(B169),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B169))</f>
         <v/>
@@ -6254,7 +6275,7 @@
       <c r="F169" s="14"/>
       <c r="G169" s="46"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="73" t="str">
         <f>IF(ISBLANK(B170),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B170))</f>
         <v/>
@@ -6266,7 +6287,7 @@
       <c r="F170" s="13"/>
       <c r="G170" s="45"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="74" t="str">
         <f>IF(ISBLANK(B171),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B171))</f>
         <v/>
@@ -6278,7 +6299,7 @@
       <c r="F171" s="14"/>
       <c r="G171" s="46"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="73" t="str">
         <f>IF(ISBLANK(B172),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B172))</f>
         <v/>
@@ -6290,7 +6311,7 @@
       <c r="F172" s="13"/>
       <c r="G172" s="45"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="74" t="str">
         <f>IF(ISBLANK(B173),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B173))</f>
         <v/>
@@ -6302,7 +6323,7 @@
       <c r="F173" s="14"/>
       <c r="G173" s="46"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="73" t="str">
         <f>IF(ISBLANK(B174),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B174))</f>
         <v/>
@@ -6314,7 +6335,7 @@
       <c r="F174" s="13"/>
       <c r="G174" s="45"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="74" t="str">
         <f>IF(ISBLANK(B175),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B175))</f>
         <v/>
@@ -6326,7 +6347,7 @@
       <c r="F175" s="14"/>
       <c r="G175" s="46"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="73" t="str">
         <f>IF(ISBLANK(B176),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B176))</f>
         <v/>
@@ -6338,7 +6359,7 @@
       <c r="F176" s="13"/>
       <c r="G176" s="45"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="74" t="str">
         <f>IF(ISBLANK(B177),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B177))</f>
         <v/>
@@ -6350,7 +6371,7 @@
       <c r="F177" s="14"/>
       <c r="G177" s="46"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="73" t="str">
         <f>IF(ISBLANK(B178),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B178))</f>
         <v/>
@@ -6362,7 +6383,7 @@
       <c r="F178" s="13"/>
       <c r="G178" s="45"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="74" t="str">
         <f>IF(ISBLANK(B179),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B179))</f>
         <v/>
@@ -6374,7 +6395,7 @@
       <c r="F179" s="14"/>
       <c r="G179" s="46"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="73" t="str">
         <f>IF(ISBLANK(B180),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B180))</f>
         <v/>
@@ -6386,7 +6407,7 @@
       <c r="F180" s="13"/>
       <c r="G180" s="45"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="74" t="str">
         <f>IF(ISBLANK(B181),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B181))</f>
         <v/>
@@ -6398,7 +6419,7 @@
       <c r="F181" s="14"/>
       <c r="G181" s="46"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="73" t="str">
         <f>IF(ISBLANK(B182),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B182))</f>
         <v/>
@@ -6410,7 +6431,7 @@
       <c r="F182" s="13"/>
       <c r="G182" s="45"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="74" t="str">
         <f>IF(ISBLANK(B183),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B183))</f>
         <v/>
@@ -6422,7 +6443,7 @@
       <c r="F183" s="14"/>
       <c r="G183" s="46"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="73" t="str">
         <f>IF(ISBLANK(B184),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B184))</f>
         <v/>
@@ -6434,7 +6455,7 @@
       <c r="F184" s="13"/>
       <c r="G184" s="45"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="74" t="str">
         <f>IF(ISBLANK(B185),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B185))</f>
         <v/>
@@ -6446,7 +6467,7 @@
       <c r="F185" s="14"/>
       <c r="G185" s="46"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="73" t="str">
         <f>IF(ISBLANK(B186),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B186))</f>
         <v/>
@@ -6458,7 +6479,7 @@
       <c r="F186" s="13"/>
       <c r="G186" s="45"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="74" t="str">
         <f>IF(ISBLANK(B187),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B187))</f>
         <v/>
@@ -6470,7 +6491,7 @@
       <c r="F187" s="14"/>
       <c r="G187" s="46"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="73" t="str">
         <f>IF(ISBLANK(B188),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B188))</f>
         <v/>
@@ -6482,7 +6503,7 @@
       <c r="F188" s="13"/>
       <c r="G188" s="45"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="74" t="str">
         <f>IF(ISBLANK(B189),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B189))</f>
         <v/>
@@ -6494,7 +6515,7 @@
       <c r="F189" s="14"/>
       <c r="G189" s="46"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="73" t="str">
         <f>IF(ISBLANK(B190),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B190))</f>
         <v/>
@@ -6506,7 +6527,7 @@
       <c r="F190" s="13"/>
       <c r="G190" s="45"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="74" t="str">
         <f>IF(ISBLANK(B191),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B191))</f>
         <v/>
@@ -6518,7 +6539,7 @@
       <c r="F191" s="14"/>
       <c r="G191" s="46"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="73" t="str">
         <f>IF(ISBLANK(B192),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B192))</f>
         <v/>
@@ -6530,7 +6551,7 @@
       <c r="F192" s="13"/>
       <c r="G192" s="45"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="74" t="str">
         <f>IF(ISBLANK(B193),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B193))</f>
         <v/>
@@ -6542,7 +6563,7 @@
       <c r="F193" s="14"/>
       <c r="G193" s="46"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="73" t="str">
         <f>IF(ISBLANK(B194),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B194))</f>
         <v/>
@@ -6554,7 +6575,7 @@
       <c r="F194" s="13"/>
       <c r="G194" s="45"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="74" t="str">
         <f>IF(ISBLANK(B195),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B195))</f>
         <v/>
@@ -6566,7 +6587,7 @@
       <c r="F195" s="14"/>
       <c r="G195" s="46"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="73" t="str">
         <f>IF(ISBLANK(B196),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B196))</f>
         <v/>
@@ -6578,7 +6599,7 @@
       <c r="F196" s="13"/>
       <c r="G196" s="45"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="74" t="str">
         <f>IF(ISBLANK(B197),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B197))</f>
         <v/>
@@ -6590,7 +6611,7 @@
       <c r="F197" s="14"/>
       <c r="G197" s="46"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="73" t="str">
         <f>IF(ISBLANK(B198),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B198))</f>
         <v/>
@@ -6602,7 +6623,7 @@
       <c r="F198" s="13"/>
       <c r="G198" s="45"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="74" t="str">
         <f>IF(ISBLANK(B199),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B199))</f>
         <v/>
@@ -6614,7 +6635,7 @@
       <c r="F199" s="14"/>
       <c r="G199" s="46"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="73" t="str">
         <f>IF(ISBLANK(B200),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B200))</f>
         <v/>
@@ -6626,7 +6647,7 @@
       <c r="F200" s="13"/>
       <c r="G200" s="45"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="74" t="str">
         <f>IF(ISBLANK(B201),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B201))</f>
         <v/>
@@ -6638,7 +6659,7 @@
       <c r="F201" s="14"/>
       <c r="G201" s="46"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="73" t="str">
         <f>IF(ISBLANK(B202),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B202))</f>
         <v/>
@@ -6650,7 +6671,7 @@
       <c r="F202" s="13"/>
       <c r="G202" s="45"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="74" t="str">
         <f>IF(ISBLANK(B203),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B203))</f>
         <v/>
@@ -6662,7 +6683,7 @@
       <c r="F203" s="14"/>
       <c r="G203" s="46"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="73" t="str">
         <f>IF(ISBLANK(B204),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B204))</f>
         <v/>
@@ -6674,7 +6695,7 @@
       <c r="F204" s="13"/>
       <c r="G204" s="45"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="74" t="str">
         <f>IF(ISBLANK(B205),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B205))</f>
         <v/>
@@ -6686,7 +6707,7 @@
       <c r="F205" s="14"/>
       <c r="G205" s="46"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="73" t="str">
         <f>IF(ISBLANK(B206),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B206))</f>
         <v/>
@@ -6698,7 +6719,7 @@
       <c r="F206" s="13"/>
       <c r="G206" s="45"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="74" t="str">
         <f>IF(ISBLANK(B207),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B207))</f>
         <v/>
@@ -6710,7 +6731,7 @@
       <c r="F207" s="14"/>
       <c r="G207" s="46"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="73" t="str">
         <f>IF(ISBLANK(B208),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B208))</f>
         <v/>
@@ -6722,7 +6743,7 @@
       <c r="F208" s="13"/>
       <c r="G208" s="45"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="74" t="str">
         <f>IF(ISBLANK(B209),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B209))</f>
         <v/>
@@ -6734,7 +6755,7 @@
       <c r="F209" s="14"/>
       <c r="G209" s="46"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="73" t="str">
         <f>IF(ISBLANK(B210),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B210))</f>
         <v/>
@@ -6746,7 +6767,7 @@
       <c r="F210" s="13"/>
       <c r="G210" s="45"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="74" t="str">
         <f>IF(ISBLANK(B211),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B211))</f>
         <v/>
@@ -6758,7 +6779,7 @@
       <c r="F211" s="14"/>
       <c r="G211" s="46"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="73" t="str">
         <f>IF(ISBLANK(B212),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B212))</f>
         <v/>
@@ -6770,7 +6791,7 @@
       <c r="F212" s="13"/>
       <c r="G212" s="45"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="74" t="str">
         <f>IF(ISBLANK(B213),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B213))</f>
         <v/>
@@ -6782,7 +6803,7 @@
       <c r="F213" s="14"/>
       <c r="G213" s="46"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="73" t="str">
         <f>IF(ISBLANK(B214),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B214))</f>
         <v/>
@@ -6794,7 +6815,7 @@
       <c r="F214" s="13"/>
       <c r="G214" s="45"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="74" t="str">
         <f>IF(ISBLANK(B215),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B215))</f>
         <v/>
@@ -6806,7 +6827,7 @@
       <c r="F215" s="14"/>
       <c r="G215" s="46"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="73" t="str">
         <f>IF(ISBLANK(B216),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B216))</f>
         <v/>
@@ -6818,7 +6839,7 @@
       <c r="F216" s="13"/>
       <c r="G216" s="45"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="74" t="str">
         <f>IF(ISBLANK(B217),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B217))</f>
         <v/>
@@ -6830,7 +6851,7 @@
       <c r="F217" s="14"/>
       <c r="G217" s="46"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="73" t="str">
         <f>IF(ISBLANK(B218),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B218))</f>
         <v/>
@@ -6842,7 +6863,7 @@
       <c r="F218" s="13"/>
       <c r="G218" s="45"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="74" t="str">
         <f>IF(ISBLANK(B219),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B219))</f>
         <v/>
@@ -6854,7 +6875,7 @@
       <c r="F219" s="14"/>
       <c r="G219" s="46"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="73" t="str">
         <f>IF(ISBLANK(B220),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B220))</f>
         <v/>
@@ -6866,7 +6887,7 @@
       <c r="F220" s="13"/>
       <c r="G220" s="45"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="74" t="str">
         <f>IF(ISBLANK(B221),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B221))</f>
         <v/>
@@ -6878,7 +6899,7 @@
       <c r="F221" s="14"/>
       <c r="G221" s="46"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="73" t="str">
         <f>IF(ISBLANK(B222),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B222))</f>
         <v/>
@@ -6890,7 +6911,7 @@
       <c r="F222" s="13"/>
       <c r="G222" s="45"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="74" t="str">
         <f>IF(ISBLANK(B223),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B223))</f>
         <v/>
@@ -6902,7 +6923,7 @@
       <c r="F223" s="14"/>
       <c r="G223" s="46"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="73" t="str">
         <f>IF(ISBLANK(B224),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B224))</f>
         <v/>
@@ -6914,7 +6935,7 @@
       <c r="F224" s="13"/>
       <c r="G224" s="45"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="74" t="str">
         <f>IF(ISBLANK(B225),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B225))</f>
         <v/>
@@ -6926,7 +6947,7 @@
       <c r="F225" s="14"/>
       <c r="G225" s="46"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="73" t="str">
         <f>IF(ISBLANK(B226),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B226))</f>
         <v/>
@@ -6938,7 +6959,7 @@
       <c r="F226" s="13"/>
       <c r="G226" s="45"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="74" t="str">
         <f>IF(ISBLANK(B227),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B227))</f>
         <v/>
@@ -6950,7 +6971,7 @@
       <c r="F227" s="14"/>
       <c r="G227" s="46"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="73" t="str">
         <f>IF(ISBLANK(B228),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B228))</f>
         <v/>
@@ -6962,7 +6983,7 @@
       <c r="F228" s="13"/>
       <c r="G228" s="45"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="74" t="str">
         <f>IF(ISBLANK(B229),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B229))</f>
         <v/>
@@ -6974,7 +6995,7 @@
       <c r="F229" s="14"/>
       <c r="G229" s="46"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="73" t="str">
         <f>IF(ISBLANK(B230),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B230))</f>
         <v/>
@@ -6986,7 +7007,7 @@
       <c r="F230" s="13"/>
       <c r="G230" s="45"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="74" t="str">
         <f>IF(ISBLANK(B231),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B231))</f>
         <v/>
@@ -6998,7 +7019,7 @@
       <c r="F231" s="14"/>
       <c r="G231" s="46"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="73" t="str">
         <f>IF(ISBLANK(B232),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B232))</f>
         <v/>
@@ -7010,7 +7031,7 @@
       <c r="F232" s="13"/>
       <c r="G232" s="45"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="74" t="str">
         <f>IF(ISBLANK(B233),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B233))</f>
         <v/>
@@ -7022,7 +7043,7 @@
       <c r="F233" s="14"/>
       <c r="G233" s="46"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="73" t="str">
         <f>IF(ISBLANK(B234),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B234))</f>
         <v/>
@@ -7034,7 +7055,7 @@
       <c r="F234" s="13"/>
       <c r="G234" s="45"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="74" t="str">
         <f>IF(ISBLANK(B235),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B235))</f>
         <v/>
@@ -7046,7 +7067,7 @@
       <c r="F235" s="14"/>
       <c r="G235" s="46"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="73" t="str">
         <f>IF(ISBLANK(B236),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B236))</f>
         <v/>
@@ -7058,7 +7079,7 @@
       <c r="F236" s="13"/>
       <c r="G236" s="45"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="74" t="str">
         <f>IF(ISBLANK(B237),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B237))</f>
         <v/>
@@ -7070,7 +7091,7 @@
       <c r="F237" s="14"/>
       <c r="G237" s="46"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="73" t="str">
         <f>IF(ISBLANK(B238),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B238))</f>
         <v/>
@@ -7082,7 +7103,7 @@
       <c r="F238" s="13"/>
       <c r="G238" s="45"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="74" t="str">
         <f>IF(ISBLANK(B239),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B239))</f>
         <v/>
@@ -7094,7 +7115,7 @@
       <c r="F239" s="14"/>
       <c r="G239" s="46"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="73" t="str">
         <f>IF(ISBLANK(B240),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B240))</f>
         <v/>
@@ -7106,7 +7127,7 @@
       <c r="F240" s="13"/>
       <c r="G240" s="45"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="74" t="str">
         <f>IF(ISBLANK(B241),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B241))</f>
         <v/>
@@ -7118,7 +7139,7 @@
       <c r="F241" s="14"/>
       <c r="G241" s="46"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="73" t="str">
         <f>IF(ISBLANK(B242),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B242))</f>
         <v/>
@@ -7130,7 +7151,7 @@
       <c r="F242" s="13"/>
       <c r="G242" s="45"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="74" t="str">
         <f>IF(ISBLANK(B243),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B243))</f>
         <v/>
@@ -7142,7 +7163,7 @@
       <c r="F243" s="14"/>
       <c r="G243" s="46"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="73" t="str">
         <f>IF(ISBLANK(B244),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B244))</f>
         <v/>
@@ -7154,7 +7175,7 @@
       <c r="F244" s="13"/>
       <c r="G244" s="45"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="74" t="str">
         <f>IF(ISBLANK(B245),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B245))</f>
         <v/>
@@ -7166,7 +7187,7 @@
       <c r="F245" s="14"/>
       <c r="G245" s="46"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="73" t="str">
         <f>IF(ISBLANK(B246),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B246))</f>
         <v/>
@@ -7178,7 +7199,7 @@
       <c r="F246" s="13"/>
       <c r="G246" s="45"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="74" t="str">
         <f>IF(ISBLANK(B247),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B247))</f>
         <v/>
@@ -7190,7 +7211,7 @@
       <c r="F247" s="14"/>
       <c r="G247" s="46"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="73" t="str">
         <f>IF(ISBLANK(B248),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B248))</f>
         <v/>
@@ -7202,7 +7223,7 @@
       <c r="F248" s="13"/>
       <c r="G248" s="45"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" s="74" t="str">
         <f>IF(ISBLANK(B249),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B249))</f>
         <v/>
@@ -7214,7 +7235,7 @@
       <c r="F249" s="14"/>
       <c r="G249" s="46"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" s="73" t="str">
         <f>IF(ISBLANK(B250),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B250))</f>
         <v/>
@@ -7226,7 +7247,7 @@
       <c r="F250" s="13"/>
       <c r="G250" s="45"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" s="74" t="str">
         <f>IF(ISBLANK(B251),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B251))</f>
         <v/>
@@ -7238,7 +7259,7 @@
       <c r="F251" s="14"/>
       <c r="G251" s="46"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" s="73" t="str">
         <f>IF(ISBLANK(B252),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B252))</f>
         <v/>
@@ -7250,7 +7271,7 @@
       <c r="F252" s="13"/>
       <c r="G252" s="45"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="74" t="str">
         <f>IF(ISBLANK(B253),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B253))</f>
         <v/>
@@ -7262,7 +7283,7 @@
       <c r="F253" s="14"/>
       <c r="G253" s="46"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="73" t="str">
         <f>IF(ISBLANK(B254),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B254))</f>
         <v/>
@@ -7274,7 +7295,7 @@
       <c r="F254" s="13"/>
       <c r="G254" s="45"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="74" t="str">
         <f>IF(ISBLANK(B255),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B255))</f>
         <v/>
@@ -7286,7 +7307,7 @@
       <c r="F255" s="14"/>
       <c r="G255" s="46"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="73" t="str">
         <f>IF(ISBLANK(B256),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B256))</f>
         <v/>
@@ -7298,7 +7319,7 @@
       <c r="F256" s="13"/>
       <c r="G256" s="45"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="74" t="str">
         <f>IF(ISBLANK(B257),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B257))</f>
         <v/>
@@ -7310,7 +7331,7 @@
       <c r="F257" s="14"/>
       <c r="G257" s="46"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="73" t="str">
         <f>IF(ISBLANK(B258),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B258))</f>
         <v/>
@@ -7322,7 +7343,7 @@
       <c r="F258" s="13"/>
       <c r="G258" s="45"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="74" t="str">
         <f>IF(ISBLANK(B259),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B259))</f>
         <v/>
@@ -7334,7 +7355,7 @@
       <c r="F259" s="14"/>
       <c r="G259" s="46"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" s="73" t="str">
         <f>IF(ISBLANK(B260),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B260))</f>
         <v/>
@@ -7346,7 +7367,7 @@
       <c r="F260" s="13"/>
       <c r="G260" s="45"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="74" t="str">
         <f>IF(ISBLANK(B261),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B261))</f>
         <v/>
@@ -7358,7 +7379,7 @@
       <c r="F261" s="14"/>
       <c r="G261" s="46"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="73" t="str">
         <f>IF(ISBLANK(B262),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B262))</f>
         <v/>
@@ -7370,7 +7391,7 @@
       <c r="F262" s="13"/>
       <c r="G262" s="45"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" s="74" t="str">
         <f>IF(ISBLANK(B263),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B263))</f>
         <v/>
@@ -7382,7 +7403,7 @@
       <c r="F263" s="14"/>
       <c r="G263" s="46"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" s="73" t="str">
         <f>IF(ISBLANK(B264),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B264))</f>
         <v/>
@@ -7394,7 +7415,7 @@
       <c r="F264" s="13"/>
       <c r="G264" s="45"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="74" t="str">
         <f>IF(ISBLANK(B265),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B265))</f>
         <v/>
@@ -7406,7 +7427,7 @@
       <c r="F265" s="14"/>
       <c r="G265" s="46"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="73" t="str">
         <f>IF(ISBLANK(B266),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B266))</f>
         <v/>
@@ -7418,7 +7439,7 @@
       <c r="F266" s="13"/>
       <c r="G266" s="45"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="74" t="str">
         <f>IF(ISBLANK(B267),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B267))</f>
         <v/>
@@ -7430,7 +7451,7 @@
       <c r="F267" s="14"/>
       <c r="G267" s="46"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="73" t="str">
         <f>IF(ISBLANK(B268),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B268))</f>
         <v/>
@@ -7442,7 +7463,7 @@
       <c r="F268" s="13"/>
       <c r="G268" s="45"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="74" t="str">
         <f>IF(ISBLANK(B269),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B269))</f>
         <v/>
@@ -7454,7 +7475,7 @@
       <c r="F269" s="14"/>
       <c r="G269" s="46"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="73" t="str">
         <f>IF(ISBLANK(B270),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B270))</f>
         <v/>
@@ -7466,7 +7487,7 @@
       <c r="F270" s="13"/>
       <c r="G270" s="45"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" s="74" t="str">
         <f>IF(ISBLANK(B271),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B271))</f>
         <v/>
@@ -7478,7 +7499,7 @@
       <c r="F271" s="14"/>
       <c r="G271" s="46"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" s="73" t="str">
         <f>IF(ISBLANK(B272),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B272))</f>
         <v/>
@@ -7490,7 +7511,7 @@
       <c r="F272" s="13"/>
       <c r="G272" s="45"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="74" t="str">
         <f>IF(ISBLANK(B273),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B273))</f>
         <v/>
@@ -7502,7 +7523,7 @@
       <c r="F273" s="14"/>
       <c r="G273" s="46"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="73" t="str">
         <f>IF(ISBLANK(B274),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B274))</f>
         <v/>
@@ -7514,7 +7535,7 @@
       <c r="F274" s="13"/>
       <c r="G274" s="45"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="74" t="str">
         <f>IF(ISBLANK(B275),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B275))</f>
         <v/>
@@ -7526,7 +7547,7 @@
       <c r="F275" s="14"/>
       <c r="G275" s="46"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="73" t="str">
         <f>IF(ISBLANK(B276),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B276))</f>
         <v/>
@@ -7538,7 +7559,7 @@
       <c r="F276" s="13"/>
       <c r="G276" s="45"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="74" t="str">
         <f>IF(ISBLANK(B277),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B277))</f>
         <v/>
@@ -7550,7 +7571,7 @@
       <c r="F277" s="14"/>
       <c r="G277" s="46"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="73" t="str">
         <f>IF(ISBLANK(B278),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B278))</f>
         <v/>
@@ -7562,7 +7583,7 @@
       <c r="F278" s="13"/>
       <c r="G278" s="45"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="74" t="str">
         <f>IF(ISBLANK(B279),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B279))</f>
         <v/>
@@ -7574,7 +7595,7 @@
       <c r="F279" s="14"/>
       <c r="G279" s="46"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="73" t="str">
         <f>IF(ISBLANK(B280),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B280))</f>
         <v/>
@@ -7586,7 +7607,7 @@
       <c r="F280" s="13"/>
       <c r="G280" s="45"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="74" t="str">
         <f>IF(ISBLANK(B281),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B281))</f>
         <v/>
@@ -7598,7 +7619,7 @@
       <c r="F281" s="14"/>
       <c r="G281" s="46"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="73" t="str">
         <f>IF(ISBLANK(B282),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B282))</f>
         <v/>
@@ -7610,7 +7631,7 @@
       <c r="F282" s="13"/>
       <c r="G282" s="45"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="74" t="str">
         <f>IF(ISBLANK(B283),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B283))</f>
         <v/>
@@ -7622,7 +7643,7 @@
       <c r="F283" s="14"/>
       <c r="G283" s="46"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="73" t="str">
         <f>IF(ISBLANK(B284),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B284))</f>
         <v/>
@@ -7634,7 +7655,7 @@
       <c r="F284" s="13"/>
       <c r="G284" s="45"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="74" t="str">
         <f>IF(ISBLANK(B285),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B285))</f>
         <v/>
@@ -7646,7 +7667,7 @@
       <c r="F285" s="14"/>
       <c r="G285" s="46"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="73" t="str">
         <f>IF(ISBLANK(B286),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B286))</f>
         <v/>
@@ -7658,7 +7679,7 @@
       <c r="F286" s="13"/>
       <c r="G286" s="45"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="74" t="str">
         <f>IF(ISBLANK(B287),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B287))</f>
         <v/>
@@ -7670,7 +7691,7 @@
       <c r="F287" s="14"/>
       <c r="G287" s="46"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="73" t="str">
         <f>IF(ISBLANK(B288),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B288))</f>
         <v/>
@@ -7682,7 +7703,7 @@
       <c r="F288" s="13"/>
       <c r="G288" s="45"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="74" t="str">
         <f>IF(ISBLANK(B289),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B289))</f>
         <v/>
@@ -7694,7 +7715,7 @@
       <c r="F289" s="14"/>
       <c r="G289" s="46"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="73" t="str">
         <f>IF(ISBLANK(B290),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B290))</f>
         <v/>
@@ -7706,7 +7727,7 @@
       <c r="F290" s="13"/>
       <c r="G290" s="45"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" s="74" t="str">
         <f>IF(ISBLANK(B291),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B291))</f>
         <v/>
@@ -7718,7 +7739,7 @@
       <c r="F291" s="14"/>
       <c r="G291" s="46"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="73" t="str">
         <f>IF(ISBLANK(B292),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B292))</f>
         <v/>
@@ -7730,7 +7751,7 @@
       <c r="F292" s="13"/>
       <c r="G292" s="45"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="74" t="str">
         <f>IF(ISBLANK(B293),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B293))</f>
         <v/>
@@ -7742,7 +7763,7 @@
       <c r="F293" s="14"/>
       <c r="G293" s="46"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" s="73" t="str">
         <f>IF(ISBLANK(B294),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B294))</f>
         <v/>
@@ -7754,7 +7775,7 @@
       <c r="F294" s="13"/>
       <c r="G294" s="45"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="74" t="str">
         <f>IF(ISBLANK(B295),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B295))</f>
         <v/>
@@ -7766,7 +7787,7 @@
       <c r="F295" s="14"/>
       <c r="G295" s="46"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="73" t="str">
         <f>IF(ISBLANK(B296),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B296))</f>
         <v/>
@@ -7778,7 +7799,7 @@
       <c r="F296" s="13"/>
       <c r="G296" s="45"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="74" t="str">
         <f>IF(ISBLANK(B297),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B297))</f>
         <v/>
@@ -7790,7 +7811,7 @@
       <c r="F297" s="14"/>
       <c r="G297" s="46"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="73" t="str">
         <f>IF(ISBLANK(B298),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B298))</f>
         <v/>
@@ -7802,7 +7823,7 @@
       <c r="F298" s="13"/>
       <c r="G298" s="45"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="74" t="str">
         <f>IF(ISBLANK(B299),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B299))</f>
         <v/>
@@ -7814,7 +7835,7 @@
       <c r="F299" s="14"/>
       <c r="G299" s="46"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="73" t="str">
         <f>IF(ISBLANK(B300),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B300))</f>
         <v/>
@@ -7826,7 +7847,7 @@
       <c r="F300" s="13"/>
       <c r="G300" s="45"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="74" t="str">
         <f>IF(ISBLANK(B301),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B301))</f>
         <v/>
@@ -7838,7 +7859,7 @@
       <c r="F301" s="14"/>
       <c r="G301" s="46"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="73" t="str">
         <f>IF(ISBLANK(B302),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B302))</f>
         <v/>
@@ -7850,7 +7871,7 @@
       <c r="F302" s="13"/>
       <c r="G302" s="45"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="74" t="str">
         <f>IF(ISBLANK(B303),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B303))</f>
         <v/>
@@ -7862,7 +7883,7 @@
       <c r="F303" s="14"/>
       <c r="G303" s="46"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="73" t="str">
         <f>IF(ISBLANK(B304),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B304))</f>
         <v/>
@@ -7874,7 +7895,7 @@
       <c r="F304" s="13"/>
       <c r="G304" s="45"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="74" t="str">
         <f>IF(ISBLANK(B305),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B305))</f>
         <v/>
@@ -7886,7 +7907,7 @@
       <c r="F305" s="14"/>
       <c r="G305" s="46"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="73" t="str">
         <f>IF(ISBLANK(B306),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B306))</f>
         <v/>
@@ -7898,7 +7919,7 @@
       <c r="F306" s="13"/>
       <c r="G306" s="45"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="74" t="str">
         <f>IF(ISBLANK(B307),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B307))</f>
         <v/>
@@ -7910,7 +7931,7 @@
       <c r="F307" s="14"/>
       <c r="G307" s="46"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="73" t="str">
         <f>IF(ISBLANK(B308),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B308))</f>
         <v/>
@@ -7922,7 +7943,7 @@
       <c r="F308" s="13"/>
       <c r="G308" s="45"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="74" t="str">
         <f>IF(ISBLANK(B309),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B309))</f>
         <v/>
@@ -7934,7 +7955,7 @@
       <c r="F309" s="14"/>
       <c r="G309" s="46"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="73" t="str">
         <f>IF(ISBLANK(B310),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B310))</f>
         <v/>
@@ -7946,7 +7967,7 @@
       <c r="F310" s="13"/>
       <c r="G310" s="45"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="74" t="str">
         <f>IF(ISBLANK(B311),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B311))</f>
         <v/>
@@ -7958,7 +7979,7 @@
       <c r="F311" s="14"/>
       <c r="G311" s="46"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="73" t="str">
         <f>IF(ISBLANK(B312),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B312))</f>
         <v/>
@@ -7970,7 +7991,7 @@
       <c r="F312" s="13"/>
       <c r="G312" s="45"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="74" t="str">
         <f>IF(ISBLANK(B313),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B313))</f>
         <v/>
@@ -7982,7 +8003,7 @@
       <c r="F313" s="14"/>
       <c r="G313" s="46"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="73" t="str">
         <f>IF(ISBLANK(B314),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B314))</f>
         <v/>
@@ -7994,7 +8015,7 @@
       <c r="F314" s="13"/>
       <c r="G314" s="45"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="74" t="str">
         <f>IF(ISBLANK(B315),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B315))</f>
         <v/>
@@ -8006,7 +8027,7 @@
       <c r="F315" s="14"/>
       <c r="G315" s="46"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="73" t="str">
         <f>IF(ISBLANK(B316),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B316))</f>
         <v/>
@@ -8018,7 +8039,7 @@
       <c r="F316" s="13"/>
       <c r="G316" s="45"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="74" t="str">
         <f>IF(ISBLANK(B317),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B317))</f>
         <v/>
@@ -8030,7 +8051,7 @@
       <c r="F317" s="14"/>
       <c r="G317" s="46"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="73" t="str">
         <f>IF(ISBLANK(B318),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B318))</f>
         <v/>
@@ -8042,7 +8063,7 @@
       <c r="F318" s="13"/>
       <c r="G318" s="45"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="74" t="str">
         <f>IF(ISBLANK(B319),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B319))</f>
         <v/>
@@ -8054,7 +8075,7 @@
       <c r="F319" s="14"/>
       <c r="G319" s="46"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="73" t="str">
         <f>IF(ISBLANK(B320),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B320))</f>
         <v/>
@@ -8066,7 +8087,7 @@
       <c r="F320" s="13"/>
       <c r="G320" s="45"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="74" t="str">
         <f>IF(ISBLANK(B321),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B321))</f>
         <v/>
@@ -8078,7 +8099,7 @@
       <c r="F321" s="14"/>
       <c r="G321" s="46"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="73" t="str">
         <f>IF(ISBLANK(B322),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B322))</f>
         <v/>
@@ -8090,7 +8111,7 @@
       <c r="F322" s="13"/>
       <c r="G322" s="45"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="74" t="str">
         <f>IF(ISBLANK(B323),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B323))</f>
         <v/>
@@ -8102,7 +8123,7 @@
       <c r="F323" s="14"/>
       <c r="G323" s="46"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="73" t="str">
         <f>IF(ISBLANK(B324),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B324))</f>
         <v/>
@@ -8114,7 +8135,7 @@
       <c r="F324" s="13"/>
       <c r="G324" s="45"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="74" t="str">
         <f>IF(ISBLANK(B325),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B325))</f>
         <v/>
@@ -8126,7 +8147,7 @@
       <c r="F325" s="14"/>
       <c r="G325" s="46"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="73" t="str">
         <f>IF(ISBLANK(B326),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B326))</f>
         <v/>
@@ -8138,7 +8159,7 @@
       <c r="F326" s="13"/>
       <c r="G326" s="45"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="74" t="str">
         <f>IF(ISBLANK(B327),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B327))</f>
         <v/>
@@ -8150,7 +8171,7 @@
       <c r="F327" s="14"/>
       <c r="G327" s="46"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="73" t="str">
         <f>IF(ISBLANK(B328),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B328))</f>
         <v/>
@@ -8162,7 +8183,7 @@
       <c r="F328" s="13"/>
       <c r="G328" s="45"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="74" t="str">
         <f>IF(ISBLANK(B329),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B329))</f>
         <v/>
@@ -8174,7 +8195,7 @@
       <c r="F329" s="14"/>
       <c r="G329" s="46"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="73" t="str">
         <f>IF(ISBLANK(B330),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B330))</f>
         <v/>
@@ -8186,7 +8207,7 @@
       <c r="F330" s="13"/>
       <c r="G330" s="45"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="74" t="str">
         <f>IF(ISBLANK(B331),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B331))</f>
         <v/>
@@ -8198,7 +8219,7 @@
       <c r="F331" s="14"/>
       <c r="G331" s="46"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="73" t="str">
         <f>IF(ISBLANK(B332),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B332))</f>
         <v/>
@@ -8210,7 +8231,7 @@
       <c r="F332" s="13"/>
       <c r="G332" s="45"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="74" t="str">
         <f>IF(ISBLANK(B333),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B333))</f>
         <v/>
@@ -8222,7 +8243,7 @@
       <c r="F333" s="14"/>
       <c r="G333" s="46"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="73" t="str">
         <f>IF(ISBLANK(B334),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B334))</f>
         <v/>
@@ -8234,7 +8255,7 @@
       <c r="F334" s="13"/>
       <c r="G334" s="45"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="74" t="str">
         <f>IF(ISBLANK(B335),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B335))</f>
         <v/>
@@ -8246,7 +8267,7 @@
       <c r="F335" s="14"/>
       <c r="G335" s="46"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="73" t="str">
         <f>IF(ISBLANK(B336),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B336))</f>
         <v/>
@@ -8258,7 +8279,7 @@
       <c r="F336" s="13"/>
       <c r="G336" s="45"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="74" t="str">
         <f>IF(ISBLANK(B337),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B337))</f>
         <v/>
@@ -8270,7 +8291,7 @@
       <c r="F337" s="14"/>
       <c r="G337" s="46"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="73" t="str">
         <f>IF(ISBLANK(B338),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B338))</f>
         <v/>
@@ -8282,7 +8303,7 @@
       <c r="F338" s="13"/>
       <c r="G338" s="45"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="74" t="str">
         <f>IF(ISBLANK(B339),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B339))</f>
         <v/>
@@ -8294,7 +8315,7 @@
       <c r="F339" s="14"/>
       <c r="G339" s="46"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="73" t="str">
         <f>IF(ISBLANK(B340),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B340))</f>
         <v/>
@@ -8306,7 +8327,7 @@
       <c r="F340" s="13"/>
       <c r="G340" s="45"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="74" t="str">
         <f>IF(ISBLANK(B341),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B341))</f>
         <v/>
@@ -8318,7 +8339,7 @@
       <c r="F341" s="14"/>
       <c r="G341" s="46"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="73" t="str">
         <f>IF(ISBLANK(B342),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B342))</f>
         <v/>
@@ -8330,7 +8351,7 @@
       <c r="F342" s="13"/>
       <c r="G342" s="45"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="74" t="str">
         <f>IF(ISBLANK(B343),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B343))</f>
         <v/>
@@ -8342,7 +8363,7 @@
       <c r="F343" s="14"/>
       <c r="G343" s="46"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="73" t="str">
         <f>IF(ISBLANK(B344),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B344))</f>
         <v/>
@@ -8354,7 +8375,7 @@
       <c r="F344" s="13"/>
       <c r="G344" s="45"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="74" t="str">
         <f>IF(ISBLANK(B345),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B345))</f>
         <v/>
@@ -8366,7 +8387,7 @@
       <c r="F345" s="14"/>
       <c r="G345" s="46"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="73" t="str">
         <f>IF(ISBLANK(B346),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B346))</f>
         <v/>
@@ -8378,7 +8399,7 @@
       <c r="F346" s="13"/>
       <c r="G346" s="45"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="74" t="str">
         <f>IF(ISBLANK(B347),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B347))</f>
         <v/>
@@ -8390,7 +8411,7 @@
       <c r="F347" s="14"/>
       <c r="G347" s="46"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="73" t="str">
         <f>IF(ISBLANK(B348),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B348))</f>
         <v/>
@@ -8402,7 +8423,7 @@
       <c r="F348" s="13"/>
       <c r="G348" s="45"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="74" t="str">
         <f>IF(ISBLANK(B349),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B349))</f>
         <v/>
@@ -8414,7 +8435,7 @@
       <c r="F349" s="14"/>
       <c r="G349" s="46"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" s="73" t="str">
         <f>IF(ISBLANK(B350),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B350))</f>
         <v/>
@@ -8426,7 +8447,7 @@
       <c r="F350" s="13"/>
       <c r="G350" s="45"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="74" t="str">
         <f>IF(ISBLANK(B351),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B351))</f>
         <v/>
@@ -8438,7 +8459,7 @@
       <c r="F351" s="14"/>
       <c r="G351" s="46"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="73" t="str">
         <f>IF(ISBLANK(B352),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B352))</f>
         <v/>
@@ -8450,7 +8471,7 @@
       <c r="F352" s="13"/>
       <c r="G352" s="45"/>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="74" t="str">
         <f>IF(ISBLANK(B353),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B353))</f>
         <v/>
@@ -8462,7 +8483,7 @@
       <c r="F353" s="14"/>
       <c r="G353" s="46"/>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="73" t="str">
         <f>IF(ISBLANK(B354),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B354))</f>
         <v/>
@@ -8474,7 +8495,7 @@
       <c r="F354" s="13"/>
       <c r="G354" s="45"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="74" t="str">
         <f>IF(ISBLANK(B355),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B355))</f>
         <v/>
@@ -8486,7 +8507,7 @@
       <c r="F355" s="14"/>
       <c r="G355" s="46"/>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="73" t="str">
         <f>IF(ISBLANK(B356),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B356))</f>
         <v/>
@@ -8498,7 +8519,7 @@
       <c r="F356" s="13"/>
       <c r="G356" s="45"/>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="74" t="str">
         <f>IF(ISBLANK(B357),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B357))</f>
         <v/>
@@ -8510,7 +8531,7 @@
       <c r="F357" s="14"/>
       <c r="G357" s="46"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="73" t="str">
         <f>IF(ISBLANK(B358),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B358))</f>
         <v/>
@@ -8522,7 +8543,7 @@
       <c r="F358" s="13"/>
       <c r="G358" s="45"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="74" t="str">
         <f>IF(ISBLANK(B359),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B359))</f>
         <v/>
@@ -8534,7 +8555,7 @@
       <c r="F359" s="14"/>
       <c r="G359" s="46"/>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="73" t="str">
         <f>IF(ISBLANK(B360),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B360))</f>
         <v/>
@@ -8546,7 +8567,7 @@
       <c r="F360" s="13"/>
       <c r="G360" s="45"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="74" t="str">
         <f>IF(ISBLANK(B361),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B361))</f>
         <v/>
@@ -8558,7 +8579,7 @@
       <c r="F361" s="14"/>
       <c r="G361" s="46"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="73" t="str">
         <f>IF(ISBLANK(B362),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B362))</f>
         <v/>
@@ -8570,7 +8591,7 @@
       <c r="F362" s="13"/>
       <c r="G362" s="45"/>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="74" t="str">
         <f>IF(ISBLANK(B363),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B363))</f>
         <v/>
@@ -8582,7 +8603,7 @@
       <c r="F363" s="14"/>
       <c r="G363" s="46"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="73" t="str">
         <f>IF(ISBLANK(B364),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B364))</f>
         <v/>
@@ -8594,7 +8615,7 @@
       <c r="F364" s="13"/>
       <c r="G364" s="45"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="74" t="str">
         <f>IF(ISBLANK(B365),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B365))</f>
         <v/>
@@ -8606,7 +8627,7 @@
       <c r="F365" s="14"/>
       <c r="G365" s="46"/>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="73" t="str">
         <f>IF(ISBLANK(B366),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B366))</f>
         <v/>
@@ -8618,7 +8639,7 @@
       <c r="F366" s="13"/>
       <c r="G366" s="45"/>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="74" t="str">
         <f>IF(ISBLANK(B367),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B367))</f>
         <v/>
@@ -8630,7 +8651,7 @@
       <c r="F367" s="14"/>
       <c r="G367" s="46"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="73" t="str">
         <f>IF(ISBLANK(B368),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B368))</f>
         <v/>
@@ -8642,7 +8663,7 @@
       <c r="F368" s="13"/>
       <c r="G368" s="45"/>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="74" t="str">
         <f>IF(ISBLANK(B369),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B369))</f>
         <v/>
@@ -8654,7 +8675,7 @@
       <c r="F369" s="14"/>
       <c r="G369" s="46"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="73" t="str">
         <f>IF(ISBLANK(B370),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B370))</f>
         <v/>
@@ -8666,7 +8687,7 @@
       <c r="F370" s="13"/>
       <c r="G370" s="45"/>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="74" t="str">
         <f>IF(ISBLANK(B371),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B371))</f>
         <v/>
@@ -8678,7 +8699,7 @@
       <c r="F371" s="14"/>
       <c r="G371" s="46"/>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="73" t="str">
         <f>IF(ISBLANK(B372),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B372))</f>
         <v/>
@@ -8690,7 +8711,7 @@
       <c r="F372" s="13"/>
       <c r="G372" s="45"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="74" t="str">
         <f>IF(ISBLANK(B373),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B373))</f>
         <v/>
@@ -8702,7 +8723,7 @@
       <c r="F373" s="14"/>
       <c r="G373" s="46"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="73" t="str">
         <f>IF(ISBLANK(B374),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B374))</f>
         <v/>
@@ -8714,7 +8735,7 @@
       <c r="F374" s="13"/>
       <c r="G374" s="45"/>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="74" t="str">
         <f>IF(ISBLANK(B375),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B375))</f>
         <v/>
@@ -8726,7 +8747,7 @@
       <c r="F375" s="14"/>
       <c r="G375" s="46"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="73" t="str">
         <f>IF(ISBLANK(B376),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B376))</f>
         <v/>
@@ -8738,7 +8759,7 @@
       <c r="F376" s="13"/>
       <c r="G376" s="45"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="74" t="str">
         <f>IF(ISBLANK(B377),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B377))</f>
         <v/>
@@ -8750,7 +8771,7 @@
       <c r="F377" s="14"/>
       <c r="G377" s="46"/>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="73" t="str">
         <f>IF(ISBLANK(B378),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B378))</f>
         <v/>
@@ -8762,7 +8783,7 @@
       <c r="F378" s="13"/>
       <c r="G378" s="45"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="74" t="str">
         <f>IF(ISBLANK(B379),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B379))</f>
         <v/>
@@ -8774,7 +8795,7 @@
       <c r="F379" s="14"/>
       <c r="G379" s="46"/>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="73" t="str">
         <f>IF(ISBLANK(B380),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B380))</f>
         <v/>
@@ -8786,7 +8807,7 @@
       <c r="F380" s="13"/>
       <c r="G380" s="45"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="74" t="str">
         <f>IF(ISBLANK(B381),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B381))</f>
         <v/>
@@ -8798,7 +8819,7 @@
       <c r="F381" s="14"/>
       <c r="G381" s="46"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="73" t="str">
         <f>IF(ISBLANK(B382),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B382))</f>
         <v/>
@@ -8810,7 +8831,7 @@
       <c r="F382" s="13"/>
       <c r="G382" s="45"/>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="74" t="str">
         <f>IF(ISBLANK(B383),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B383))</f>
         <v/>
@@ -8822,7 +8843,7 @@
       <c r="F383" s="14"/>
       <c r="G383" s="46"/>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="73" t="str">
         <f>IF(ISBLANK(B384),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B384))</f>
         <v/>
@@ -8834,7 +8855,7 @@
       <c r="F384" s="13"/>
       <c r="G384" s="45"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="74" t="str">
         <f>IF(ISBLANK(B385),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B385))</f>
         <v/>
@@ -8846,7 +8867,7 @@
       <c r="F385" s="14"/>
       <c r="G385" s="46"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="73" t="str">
         <f>IF(ISBLANK(B386),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B386))</f>
         <v/>
@@ -8858,7 +8879,7 @@
       <c r="F386" s="13"/>
       <c r="G386" s="45"/>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="74" t="str">
         <f>IF(ISBLANK(B387),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B387))</f>
         <v/>
@@ -8870,7 +8891,7 @@
       <c r="F387" s="14"/>
       <c r="G387" s="46"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="73" t="str">
         <f>IF(ISBLANK(B388),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B388))</f>
         <v/>
@@ -8882,7 +8903,7 @@
       <c r="F388" s="13"/>
       <c r="G388" s="45"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="74" t="str">
         <f>IF(ISBLANK(B389),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B389))</f>
         <v/>
@@ -8894,7 +8915,7 @@
       <c r="F389" s="14"/>
       <c r="G389" s="46"/>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" s="73" t="str">
         <f>IF(ISBLANK(B390),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B390))</f>
         <v/>
@@ -8906,7 +8927,7 @@
       <c r="F390" s="13"/>
       <c r="G390" s="45"/>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="74" t="str">
         <f>IF(ISBLANK(B391),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B391))</f>
         <v/>
@@ -8918,7 +8939,7 @@
       <c r="F391" s="14"/>
       <c r="G391" s="46"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="73" t="str">
         <f>IF(ISBLANK(B392),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B392))</f>
         <v/>
@@ -8930,7 +8951,7 @@
       <c r="F392" s="13"/>
       <c r="G392" s="45"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="74" t="str">
         <f>IF(ISBLANK(B393),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B393))</f>
         <v/>
@@ -8942,7 +8963,7 @@
       <c r="F393" s="14"/>
       <c r="G393" s="46"/>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="73" t="str">
         <f>IF(ISBLANK(B394),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B394))</f>
         <v/>
@@ -8954,7 +8975,7 @@
       <c r="F394" s="13"/>
       <c r="G394" s="45"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="74" t="str">
         <f>IF(ISBLANK(B395),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B395))</f>
         <v/>
@@ -8966,7 +8987,7 @@
       <c r="F395" s="14"/>
       <c r="G395" s="46"/>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" s="73" t="str">
         <f>IF(ISBLANK(B396),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B396))</f>
         <v/>
@@ -8978,7 +8999,7 @@
       <c r="F396" s="13"/>
       <c r="G396" s="45"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" s="74" t="str">
         <f>IF(ISBLANK(B397),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B397))</f>
         <v/>
@@ -8990,7 +9011,7 @@
       <c r="F397" s="14"/>
       <c r="G397" s="46"/>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" s="73" t="str">
         <f>IF(ISBLANK(B398),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B398))</f>
         <v/>
@@ -9002,7 +9023,7 @@
       <c r="F398" s="13"/>
       <c r="G398" s="45"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="74" t="str">
         <f>IF(ISBLANK(B399),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B399))</f>
         <v/>
@@ -9014,7 +9035,7 @@
       <c r="F399" s="14"/>
       <c r="G399" s="46"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="73" t="str">
         <f>IF(ISBLANK(B400),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B400))</f>
         <v/>
@@ -9026,7 +9047,7 @@
       <c r="F400" s="13"/>
       <c r="G400" s="45"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="74" t="str">
         <f>IF(ISBLANK(B401),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B401))</f>
         <v/>
@@ -9038,7 +9059,7 @@
       <c r="F401" s="14"/>
       <c r="G401" s="46"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="73" t="str">
         <f>IF(ISBLANK(B402),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B402))</f>
         <v/>
@@ -9050,7 +9071,7 @@
       <c r="F402" s="13"/>
       <c r="G402" s="45"/>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="74" t="str">
         <f>IF(ISBLANK(B403),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B403))</f>
         <v/>
@@ -9062,7 +9083,7 @@
       <c r="F403" s="14"/>
       <c r="G403" s="46"/>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="73" t="str">
         <f>IF(ISBLANK(B404),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B404))</f>
         <v/>
@@ -9074,7 +9095,7 @@
       <c r="F404" s="13"/>
       <c r="G404" s="45"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" s="74" t="str">
         <f>IF(ISBLANK(B405),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B405))</f>
         <v/>
@@ -9086,7 +9107,7 @@
       <c r="F405" s="14"/>
       <c r="G405" s="46"/>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="73" t="str">
         <f>IF(ISBLANK(B406),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B406))</f>
         <v/>
@@ -9098,7 +9119,7 @@
       <c r="F406" s="13"/>
       <c r="G406" s="45"/>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="74" t="str">
         <f>IF(ISBLANK(B407),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B407))</f>
         <v/>
@@ -9110,7 +9131,7 @@
       <c r="F407" s="14"/>
       <c r="G407" s="46"/>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="73" t="str">
         <f>IF(ISBLANK(B408),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B408))</f>
         <v/>
@@ -9122,7 +9143,7 @@
       <c r="F408" s="13"/>
       <c r="G408" s="45"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409" s="74" t="str">
         <f>IF(ISBLANK(B409),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B409))</f>
         <v/>
@@ -9134,7 +9155,7 @@
       <c r="F409" s="14"/>
       <c r="G409" s="46"/>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410" s="73" t="str">
         <f>IF(ISBLANK(B410),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B410))</f>
         <v/>
@@ -9146,7 +9167,7 @@
       <c r="F410" s="13"/>
       <c r="G410" s="45"/>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="74" t="str">
         <f>IF(ISBLANK(B411),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B411))</f>
         <v/>
@@ -9158,7 +9179,7 @@
       <c r="F411" s="14"/>
       <c r="G411" s="46"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412" s="73" t="str">
         <f>IF(ISBLANK(B412),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B412))</f>
         <v/>
@@ -9170,7 +9191,7 @@
       <c r="F412" s="13"/>
       <c r="G412" s="45"/>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="74" t="str">
         <f>IF(ISBLANK(B413),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B413))</f>
         <v/>
@@ -9182,7 +9203,7 @@
       <c r="F413" s="14"/>
       <c r="G413" s="46"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="73" t="str">
         <f>IF(ISBLANK(B414),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B414))</f>
         <v/>
@@ -9194,7 +9215,7 @@
       <c r="F414" s="13"/>
       <c r="G414" s="45"/>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="74" t="str">
         <f>IF(ISBLANK(B415),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B415))</f>
         <v/>
@@ -9206,7 +9227,7 @@
       <c r="F415" s="14"/>
       <c r="G415" s="46"/>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="73" t="str">
         <f>IF(ISBLANK(B416),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B416))</f>
         <v/>
@@ -9218,7 +9239,7 @@
       <c r="F416" s="13"/>
       <c r="G416" s="45"/>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="74" t="str">
         <f>IF(ISBLANK(B417),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B417))</f>
         <v/>
@@ -9230,7 +9251,7 @@
       <c r="F417" s="14"/>
       <c r="G417" s="46"/>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="73" t="str">
         <f>IF(ISBLANK(B418),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B418))</f>
         <v/>
@@ -9242,7 +9263,7 @@
       <c r="F418" s="13"/>
       <c r="G418" s="45"/>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="74" t="str">
         <f>IF(ISBLANK(B419),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B419))</f>
         <v/>
@@ -9254,7 +9275,7 @@
       <c r="F419" s="14"/>
       <c r="G419" s="46"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="73" t="str">
         <f>IF(ISBLANK(B420),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B420))</f>
         <v/>
@@ -9266,7 +9287,7 @@
       <c r="F420" s="13"/>
       <c r="G420" s="45"/>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="74" t="str">
         <f>IF(ISBLANK(B421),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B421))</f>
         <v/>
@@ -9278,7 +9299,7 @@
       <c r="F421" s="14"/>
       <c r="G421" s="46"/>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="73" t="str">
         <f>IF(ISBLANK(B422),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B422))</f>
         <v/>
@@ -9290,7 +9311,7 @@
       <c r="F422" s="13"/>
       <c r="G422" s="45"/>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="74" t="str">
         <f>IF(ISBLANK(B423),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B423))</f>
         <v/>
@@ -9302,7 +9323,7 @@
       <c r="F423" s="14"/>
       <c r="G423" s="46"/>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="73" t="str">
         <f>IF(ISBLANK(B424),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B424))</f>
         <v/>
@@ -9314,7 +9335,7 @@
       <c r="F424" s="13"/>
       <c r="G424" s="45"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="74" t="str">
         <f>IF(ISBLANK(B425),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B425))</f>
         <v/>
@@ -9326,7 +9347,7 @@
       <c r="F425" s="14"/>
       <c r="G425" s="46"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="73" t="str">
         <f>IF(ISBLANK(B426),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B426))</f>
         <v/>
@@ -9338,7 +9359,7 @@
       <c r="F426" s="13"/>
       <c r="G426" s="45"/>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="74" t="str">
         <f>IF(ISBLANK(B427),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B427))</f>
         <v/>
@@ -9350,7 +9371,7 @@
       <c r="F427" s="14"/>
       <c r="G427" s="46"/>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="73" t="str">
         <f>IF(ISBLANK(B428),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B428))</f>
         <v/>
@@ -9362,7 +9383,7 @@
       <c r="F428" s="13"/>
       <c r="G428" s="45"/>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="74" t="str">
         <f>IF(ISBLANK(B429),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B429))</f>
         <v/>
@@ -9374,7 +9395,7 @@
       <c r="F429" s="14"/>
       <c r="G429" s="46"/>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="73" t="str">
         <f>IF(ISBLANK(B430),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B430))</f>
         <v/>
@@ -9386,7 +9407,7 @@
       <c r="F430" s="13"/>
       <c r="G430" s="45"/>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="74" t="str">
         <f>IF(ISBLANK(B431),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B431))</f>
         <v/>
@@ -9398,7 +9419,7 @@
       <c r="F431" s="14"/>
       <c r="G431" s="46"/>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="73" t="str">
         <f>IF(ISBLANK(B432),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B432))</f>
         <v/>
@@ -9410,7 +9431,7 @@
       <c r="F432" s="13"/>
       <c r="G432" s="45"/>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="74" t="str">
         <f>IF(ISBLANK(B433),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B433))</f>
         <v/>
@@ -9422,7 +9443,7 @@
       <c r="F433" s="14"/>
       <c r="G433" s="46"/>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="73" t="str">
         <f>IF(ISBLANK(B434),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B434))</f>
         <v/>
@@ -9434,7 +9455,7 @@
       <c r="F434" s="13"/>
       <c r="G434" s="45"/>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="74" t="str">
         <f>IF(ISBLANK(B435),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B435))</f>
         <v/>
@@ -9446,7 +9467,7 @@
       <c r="F435" s="14"/>
       <c r="G435" s="46"/>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="73" t="str">
         <f>IF(ISBLANK(B436),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B436))</f>
         <v/>
@@ -9458,7 +9479,7 @@
       <c r="F436" s="13"/>
       <c r="G436" s="45"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="74" t="str">
         <f>IF(ISBLANK(B437),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B437))</f>
         <v/>
@@ -9470,7 +9491,7 @@
       <c r="F437" s="14"/>
       <c r="G437" s="46"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="73" t="str">
         <f>IF(ISBLANK(B438),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B438))</f>
         <v/>
@@ -9482,7 +9503,7 @@
       <c r="F438" s="13"/>
       <c r="G438" s="45"/>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="74" t="str">
         <f>IF(ISBLANK(B439),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B439))</f>
         <v/>
@@ -9494,7 +9515,7 @@
       <c r="F439" s="14"/>
       <c r="G439" s="46"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="73" t="str">
         <f>IF(ISBLANK(B440),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B440))</f>
         <v/>
@@ -9506,7 +9527,7 @@
       <c r="F440" s="13"/>
       <c r="G440" s="45"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="74" t="str">
         <f>IF(ISBLANK(B441),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B441))</f>
         <v/>
@@ -9518,7 +9539,7 @@
       <c r="F441" s="14"/>
       <c r="G441" s="46"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="73" t="str">
         <f>IF(ISBLANK(B442),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B442))</f>
         <v/>
@@ -9530,7 +9551,7 @@
       <c r="F442" s="13"/>
       <c r="G442" s="45"/>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="74" t="str">
         <f>IF(ISBLANK(B443),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B443))</f>
         <v/>
@@ -9542,7 +9563,7 @@
       <c r="F443" s="14"/>
       <c r="G443" s="46"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="73" t="str">
         <f>IF(ISBLANK(B444),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B444))</f>
         <v/>
@@ -9554,7 +9575,7 @@
       <c r="F444" s="13"/>
       <c r="G444" s="45"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="74" t="str">
         <f>IF(ISBLANK(B445),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B445))</f>
         <v/>
@@ -9566,7 +9587,7 @@
       <c r="F445" s="14"/>
       <c r="G445" s="46"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="73" t="str">
         <f>IF(ISBLANK(B446),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B446))</f>
         <v/>
@@ -9578,7 +9599,7 @@
       <c r="F446" s="13"/>
       <c r="G446" s="45"/>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="74" t="str">
         <f>IF(ISBLANK(B447),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B447))</f>
         <v/>
@@ -9590,7 +9611,7 @@
       <c r="F447" s="14"/>
       <c r="G447" s="46"/>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="73" t="str">
         <f>IF(ISBLANK(B448),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B448))</f>
         <v/>
@@ -9602,7 +9623,7 @@
       <c r="F448" s="13"/>
       <c r="G448" s="45"/>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="74" t="str">
         <f>IF(ISBLANK(B449),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B449))</f>
         <v/>
@@ -9614,7 +9635,7 @@
       <c r="F449" s="14"/>
       <c r="G449" s="46"/>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="73" t="str">
         <f>IF(ISBLANK(B450),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B450))</f>
         <v/>
@@ -9626,7 +9647,7 @@
       <c r="F450" s="13"/>
       <c r="G450" s="45"/>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="74" t="str">
         <f>IF(ISBLANK(B451),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B451))</f>
         <v/>
@@ -9638,7 +9659,7 @@
       <c r="F451" s="14"/>
       <c r="G451" s="46"/>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="73" t="str">
         <f>IF(ISBLANK(B452),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B452))</f>
         <v/>
@@ -9650,7 +9671,7 @@
       <c r="F452" s="13"/>
       <c r="G452" s="45"/>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="74" t="str">
         <f>IF(ISBLANK(B453),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B453))</f>
         <v/>
@@ -9662,7 +9683,7 @@
       <c r="F453" s="14"/>
       <c r="G453" s="46"/>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="73" t="str">
         <f>IF(ISBLANK(B454),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B454))</f>
         <v/>
@@ -9674,7 +9695,7 @@
       <c r="F454" s="13"/>
       <c r="G454" s="45"/>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="74" t="str">
         <f>IF(ISBLANK(B455),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B455))</f>
         <v/>
@@ -9686,7 +9707,7 @@
       <c r="F455" s="14"/>
       <c r="G455" s="46"/>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="73" t="str">
         <f>IF(ISBLANK(B456),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B456))</f>
         <v/>
@@ -9698,7 +9719,7 @@
       <c r="F456" s="13"/>
       <c r="G456" s="45"/>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="74" t="str">
         <f>IF(ISBLANK(B457),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B457))</f>
         <v/>
@@ -9710,7 +9731,7 @@
       <c r="F457" s="14"/>
       <c r="G457" s="46"/>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" s="73" t="str">
         <f>IF(ISBLANK(B458),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B458))</f>
         <v/>
@@ -9722,7 +9743,7 @@
       <c r="F458" s="13"/>
       <c r="G458" s="45"/>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="74" t="str">
         <f>IF(ISBLANK(B459),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B459))</f>
         <v/>
@@ -9734,7 +9755,7 @@
       <c r="F459" s="14"/>
       <c r="G459" s="46"/>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="73" t="str">
         <f>IF(ISBLANK(B460),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B460))</f>
         <v/>
@@ -9746,7 +9767,7 @@
       <c r="F460" s="13"/>
       <c r="G460" s="45"/>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="74" t="str">
         <f>IF(ISBLANK(B461),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B461))</f>
         <v/>
@@ -9758,7 +9779,7 @@
       <c r="F461" s="14"/>
       <c r="G461" s="46"/>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="73" t="str">
         <f>IF(ISBLANK(B462),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B462))</f>
         <v/>
@@ -9770,7 +9791,7 @@
       <c r="F462" s="13"/>
       <c r="G462" s="45"/>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="74" t="str">
         <f>IF(ISBLANK(B463),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B463))</f>
         <v/>
@@ -9782,7 +9803,7 @@
       <c r="F463" s="14"/>
       <c r="G463" s="46"/>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="73" t="str">
         <f>IF(ISBLANK(B464),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B464))</f>
         <v/>
@@ -9794,7 +9815,7 @@
       <c r="F464" s="13"/>
       <c r="G464" s="45"/>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="74" t="str">
         <f>IF(ISBLANK(B465),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B465))</f>
         <v/>
@@ -9806,7 +9827,7 @@
       <c r="F465" s="14"/>
       <c r="G465" s="46"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" s="73" t="str">
         <f>IF(ISBLANK(B466),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B466))</f>
         <v/>
@@ -9818,7 +9839,7 @@
       <c r="F466" s="13"/>
       <c r="G466" s="45"/>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467" s="74" t="str">
         <f>IF(ISBLANK(B467),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B467))</f>
         <v/>
@@ -9830,7 +9851,7 @@
       <c r="F467" s="14"/>
       <c r="G467" s="46"/>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468" s="73" t="str">
         <f>IF(ISBLANK(B468),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B468))</f>
         <v/>
@@ -9842,7 +9863,7 @@
       <c r="F468" s="13"/>
       <c r="G468" s="45"/>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="74" t="str">
         <f>IF(ISBLANK(B469),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B469))</f>
         <v/>
@@ -9854,7 +9875,7 @@
       <c r="F469" s="14"/>
       <c r="G469" s="46"/>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="73" t="str">
         <f>IF(ISBLANK(B470),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B470))</f>
         <v/>
@@ -9866,7 +9887,7 @@
       <c r="F470" s="13"/>
       <c r="G470" s="45"/>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="74" t="str">
         <f>IF(ISBLANK(B471),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B471))</f>
         <v/>
@@ -9878,7 +9899,7 @@
       <c r="F471" s="14"/>
       <c r="G471" s="46"/>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="73" t="str">
         <f>IF(ISBLANK(B472),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B472))</f>
         <v/>
@@ -9890,7 +9911,7 @@
       <c r="F472" s="13"/>
       <c r="G472" s="45"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="74" t="str">
         <f>IF(ISBLANK(B473),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B473))</f>
         <v/>
@@ -9902,7 +9923,7 @@
       <c r="F473" s="14"/>
       <c r="G473" s="46"/>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="73" t="str">
         <f>IF(ISBLANK(B474),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B474))</f>
         <v/>
@@ -9914,7 +9935,7 @@
       <c r="F474" s="13"/>
       <c r="G474" s="45"/>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475" s="74" t="str">
         <f>IF(ISBLANK(B475),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B475))</f>
         <v/>
@@ -9926,7 +9947,7 @@
       <c r="F475" s="14"/>
       <c r="G475" s="46"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476" s="73" t="str">
         <f>IF(ISBLANK(B476),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B476))</f>
         <v/>
@@ -9938,7 +9959,7 @@
       <c r="F476" s="13"/>
       <c r="G476" s="45"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="74" t="str">
         <f>IF(ISBLANK(B477),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B477))</f>
         <v/>
@@ -9950,7 +9971,7 @@
       <c r="F477" s="14"/>
       <c r="G477" s="46"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="73" t="str">
         <f>IF(ISBLANK(B478),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B478))</f>
         <v/>
@@ -9962,7 +9983,7 @@
       <c r="F478" s="13"/>
       <c r="G478" s="45"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="74" t="str">
         <f>IF(ISBLANK(B479),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B479))</f>
         <v/>
@@ -9974,7 +9995,7 @@
       <c r="F479" s="14"/>
       <c r="G479" s="46"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="73" t="str">
         <f>IF(ISBLANK(B480),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B480))</f>
         <v/>
@@ -9986,7 +10007,7 @@
       <c r="F480" s="13"/>
       <c r="G480" s="45"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="74" t="str">
         <f>IF(ISBLANK(B481),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B481))</f>
         <v/>
@@ -9998,7 +10019,7 @@
       <c r="F481" s="14"/>
       <c r="G481" s="46"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="73" t="str">
         <f>IF(ISBLANK(B482),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B482))</f>
         <v/>
@@ -10010,7 +10031,7 @@
       <c r="F482" s="13"/>
       <c r="G482" s="45"/>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="74" t="str">
         <f>IF(ISBLANK(B483),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B483))</f>
         <v/>
@@ -10022,7 +10043,7 @@
       <c r="F483" s="14"/>
       <c r="G483" s="46"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="73" t="str">
         <f>IF(ISBLANK(B484),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B484))</f>
         <v/>
@@ -10034,7 +10055,7 @@
       <c r="F484" s="13"/>
       <c r="G484" s="45"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="74" t="str">
         <f>IF(ISBLANK(B485),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B485))</f>
         <v/>
@@ -10046,7 +10067,7 @@
       <c r="F485" s="14"/>
       <c r="G485" s="46"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="73" t="str">
         <f>IF(ISBLANK(B486),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B486))</f>
         <v/>
@@ -10058,7 +10079,7 @@
       <c r="F486" s="13"/>
       <c r="G486" s="45"/>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487" s="74" t="str">
         <f>IF(ISBLANK(B487),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B487))</f>
         <v/>
@@ -10070,7 +10091,7 @@
       <c r="F487" s="14"/>
       <c r="G487" s="46"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="73" t="str">
         <f>IF(ISBLANK(B488),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B488))</f>
         <v/>
@@ -10082,7 +10103,7 @@
       <c r="F488" s="13"/>
       <c r="G488" s="45"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="74" t="str">
         <f>IF(ISBLANK(B489),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B489))</f>
         <v/>
@@ -10094,7 +10115,7 @@
       <c r="F489" s="14"/>
       <c r="G489" s="46"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="73" t="str">
         <f>IF(ISBLANK(B490),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B490))</f>
         <v/>
@@ -10106,7 +10127,7 @@
       <c r="F490" s="13"/>
       <c r="G490" s="45"/>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="74" t="str">
         <f>IF(ISBLANK(B491),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B491))</f>
         <v/>
@@ -10118,7 +10139,7 @@
       <c r="F491" s="14"/>
       <c r="G491" s="46"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="73" t="str">
         <f>IF(ISBLANK(B492),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B492))</f>
         <v/>
@@ -10130,7 +10151,7 @@
       <c r="F492" s="13"/>
       <c r="G492" s="45"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="74" t="str">
         <f>IF(ISBLANK(B493),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B493))</f>
         <v/>
@@ -10142,7 +10163,7 @@
       <c r="F493" s="14"/>
       <c r="G493" s="46"/>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="73" t="str">
         <f>IF(ISBLANK(B494),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B494))</f>
         <v/>
@@ -10154,7 +10175,7 @@
       <c r="F494" s="13"/>
       <c r="G494" s="45"/>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="74" t="str">
         <f>IF(ISBLANK(B495),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B495))</f>
         <v/>
@@ -10166,7 +10187,7 @@
       <c r="F495" s="14"/>
       <c r="G495" s="46"/>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="73" t="str">
         <f>IF(ISBLANK(B496),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B496))</f>
         <v/>
@@ -10178,7 +10199,7 @@
       <c r="F496" s="13"/>
       <c r="G496" s="45"/>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="74" t="str">
         <f>IF(ISBLANK(B497),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B497))</f>
         <v/>
@@ -10190,7 +10211,7 @@
       <c r="F497" s="14"/>
       <c r="G497" s="46"/>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="73" t="str">
         <f>IF(ISBLANK(B498),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B498))</f>
         <v/>
@@ -10202,7 +10223,7 @@
       <c r="F498" s="13"/>
       <c r="G498" s="45"/>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="74" t="str">
         <f>IF(ISBLANK(B499),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B499))</f>
         <v/>
@@ -10214,7 +10235,7 @@
       <c r="F499" s="14"/>
       <c r="G499" s="46"/>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="73" t="str">
         <f>IF(ISBLANK(B500),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B500))</f>
         <v/>
@@ -10226,7 +10247,7 @@
       <c r="F500" s="13"/>
       <c r="G500" s="45"/>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="74" t="str">
         <f>IF(ISBLANK(B501),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B501))</f>
         <v/>
@@ -10238,7 +10259,7 @@
       <c r="F501" s="14"/>
       <c r="G501" s="46"/>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="73" t="str">
         <f>IF(ISBLANK(B502),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B502))</f>
         <v/>
@@ -10250,7 +10271,7 @@
       <c r="F502" s="13"/>
       <c r="G502" s="45"/>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="74" t="str">
         <f>IF(ISBLANK(B503),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B503))</f>
         <v/>
@@ -10262,7 +10283,7 @@
       <c r="F503" s="14"/>
       <c r="G503" s="46"/>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="73" t="str">
         <f>IF(ISBLANK(B504),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B504))</f>
         <v/>
@@ -10274,7 +10295,7 @@
       <c r="F504" s="13"/>
       <c r="G504" s="45"/>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="74" t="str">
         <f>IF(ISBLANK(B505),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B505))</f>
         <v/>
@@ -10286,7 +10307,7 @@
       <c r="F505" s="14"/>
       <c r="G505" s="46"/>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="73" t="str">
         <f>IF(ISBLANK(B506),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B506))</f>
         <v/>
@@ -10298,7 +10319,7 @@
       <c r="F506" s="13"/>
       <c r="G506" s="45"/>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="74" t="str">
         <f>IF(ISBLANK(B507),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B507))</f>
         <v/>
@@ -10310,7 +10331,7 @@
       <c r="F507" s="14"/>
       <c r="G507" s="46"/>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="73" t="str">
         <f>IF(ISBLANK(B508),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B508))</f>
         <v/>
@@ -10322,7 +10343,7 @@
       <c r="F508" s="13"/>
       <c r="G508" s="45"/>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="74" t="str">
         <f>IF(ISBLANK(B509),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B509))</f>
         <v/>
@@ -10334,7 +10355,7 @@
       <c r="F509" s="14"/>
       <c r="G509" s="46"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="73" t="str">
         <f>IF(ISBLANK(B510),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B510))</f>
         <v/>
@@ -10346,7 +10367,7 @@
       <c r="F510" s="13"/>
       <c r="G510" s="45"/>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="74" t="str">
         <f>IF(ISBLANK(B511),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B511))</f>
         <v/>
@@ -10358,7 +10379,7 @@
       <c r="F511" s="14"/>
       <c r="G511" s="46"/>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="73" t="str">
         <f>IF(ISBLANK(B512),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B512))</f>
         <v/>
@@ -10370,7 +10391,7 @@
       <c r="F512" s="13"/>
       <c r="G512" s="45"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="74" t="str">
         <f>IF(ISBLANK(B513),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B513))</f>
         <v/>
@@ -10382,7 +10403,7 @@
       <c r="F513" s="14"/>
       <c r="G513" s="46"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="73" t="str">
         <f>IF(ISBLANK(B514),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B514))</f>
         <v/>
@@ -10394,7 +10415,7 @@
       <c r="F514" s="13"/>
       <c r="G514" s="45"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="74" t="str">
         <f>IF(ISBLANK(B515),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B515))</f>
         <v/>
@@ -10406,7 +10427,7 @@
       <c r="F515" s="14"/>
       <c r="G515" s="46"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="73" t="str">
         <f>IF(ISBLANK(B516),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B516))</f>
         <v/>
@@ -10418,7 +10439,7 @@
       <c r="F516" s="13"/>
       <c r="G516" s="45"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="74" t="str">
         <f>IF(ISBLANK(B517),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B517))</f>
         <v/>
@@ -10430,7 +10451,7 @@
       <c r="F517" s="14"/>
       <c r="G517" s="46"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="73" t="str">
         <f>IF(ISBLANK(B518),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B518))</f>
         <v/>
@@ -10442,7 +10463,7 @@
       <c r="F518" s="13"/>
       <c r="G518" s="45"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="74" t="str">
         <f>IF(ISBLANK(B519),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B519))</f>
         <v/>
@@ -10454,7 +10475,7 @@
       <c r="F519" s="14"/>
       <c r="G519" s="46"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" s="73" t="str">
         <f>IF(ISBLANK(B520),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B520))</f>
         <v/>
@@ -10466,7 +10487,7 @@
       <c r="F520" s="13"/>
       <c r="G520" s="45"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" s="74" t="str">
         <f>IF(ISBLANK(B521),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B521))</f>
         <v/>
@@ -10478,7 +10499,7 @@
       <c r="F521" s="14"/>
       <c r="G521" s="46"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" s="73" t="str">
         <f>IF(ISBLANK(B522),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B522))</f>
         <v/>
@@ -10490,7 +10511,7 @@
       <c r="F522" s="13"/>
       <c r="G522" s="45"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" s="74" t="str">
         <f>IF(ISBLANK(B523),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B523))</f>
         <v/>
@@ -10502,7 +10523,7 @@
       <c r="F523" s="14"/>
       <c r="G523" s="46"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="73" t="str">
         <f>IF(ISBLANK(B524),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B524))</f>
         <v/>
@@ -10514,7 +10535,7 @@
       <c r="F524" s="13"/>
       <c r="G524" s="45"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="74" t="str">
         <f>IF(ISBLANK(B525),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B525))</f>
         <v/>
@@ -10526,7 +10547,7 @@
       <c r="F525" s="14"/>
       <c r="G525" s="46"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" s="73" t="str">
         <f>IF(ISBLANK(B526),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B526))</f>
         <v/>
@@ -10538,7 +10559,7 @@
       <c r="F526" s="13"/>
       <c r="G526" s="45"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" s="74" t="str">
         <f>IF(ISBLANK(B527),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B527))</f>
         <v/>
@@ -10550,7 +10571,7 @@
       <c r="F527" s="14"/>
       <c r="G527" s="46"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" s="73" t="str">
         <f>IF(ISBLANK(B528),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B528))</f>
         <v/>
@@ -10562,7 +10583,7 @@
       <c r="F528" s="13"/>
       <c r="G528" s="45"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" s="74" t="str">
         <f>IF(ISBLANK(B529),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B529))</f>
         <v/>
@@ -10574,7 +10595,7 @@
       <c r="F529" s="14"/>
       <c r="G529" s="46"/>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="73" t="str">
         <f>IF(ISBLANK(B530),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B530))</f>
         <v/>
@@ -10586,7 +10607,7 @@
       <c r="F530" s="13"/>
       <c r="G530" s="45"/>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" s="74" t="str">
         <f>IF(ISBLANK(B531),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B531))</f>
         <v/>
@@ -10598,7 +10619,7 @@
       <c r="F531" s="14"/>
       <c r="G531" s="46"/>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" s="73" t="str">
         <f>IF(ISBLANK(B532),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B532))</f>
         <v/>
@@ -10667,19 +10688,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21D7432-C939-0D45-BAC2-A6A2196EA9C6}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:N12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="10.83203125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="1" max="3" width="10.875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="21" style="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5" style="48" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E2" s="77" t="s">
         <v>25</v>
       </c>
@@ -10693,12 +10714,12 @@
       <c r="M2" s="52"/>
       <c r="N2" s="20"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L3" s="24"/>
       <c r="M3" s="25"/>
       <c r="N3" s="24"/>
     </row>
-    <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E4" s="77" t="s">
         <v>26</v>
       </c>
@@ -10708,7 +10729,7 @@
       <c r="M4" s="48"/>
       <c r="N4" s="24"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -10738,7 +10759,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E6,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -10759,9 +10780,9 @@
         <f>QUOTIENT(SUM(A6:B6),60)&amp;" h "&amp;TEXT(MOD(SUM(A6:B6),60), "00")&amp;" min"</f>
         <v>0 h 00 min</v>
       </c>
-      <c r="G6" s="47" t="e">
+      <c r="G6" s="47">
         <f>SUM(A6:B6)/$C$10</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L6" s="62" t="str">
         <f>'Journal de travail'!M8</f>
@@ -10775,18 +10796,18 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10794,11 +10815,11 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>0 h 00 min</v>
-      </c>
-      <c r="G7" s="56" t="e">
+        <v>3 h 45 min</v>
+      </c>
+      <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="L7" s="64" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10812,7 +10833,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E8,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -10833,9 +10854,9 @@
         <f t="shared" si="1"/>
         <v>0 h 00 min</v>
       </c>
-      <c r="G8" s="47" t="e">
+      <c r="G8" s="47">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L8" s="65" t="str">
         <f>'Journal de travail'!M10</f>
@@ -10849,7 +10870,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E9,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -10870,9 +10891,9 @@
         <f t="shared" si="1"/>
         <v>0 h 00 min</v>
       </c>
-      <c r="G9" s="56" t="e">
+      <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="L9" s="66" t="str">
         <f>'Journal de travail'!M11</f>
@@ -10886,29 +10907,29 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>0 h 00 min</v>
+        <v>3 h 45 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0</v>
+        <v>4.261363636363636E-2</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>
@@ -10919,13 +10940,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C11">
         <f>F2*60</f>
         <v>5280</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F12" s="51"/>
     </row>
   </sheetData>
@@ -10938,7 +10959,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F31118-7D2C-C547-B9C9-EA2B04E048B8}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection algorithmName="SHA-512" hashValue="XbZXOKbfSAgLNZr8i9zbx3Mg5WERmkYtMQ92zj4MzR65FvyWSSvnn71Zle3H3OLpYxxTtkJ9EnrqgX4Va8ga5w==" saltValue="TZrTQ2fJcSarc1EkKUon9w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10947,27 +10968,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11180,10 +11180,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
+    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11202,5 +11234,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E45D77-D6F4-4BB0-BFBA-5B261372BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE45E312-BC82-452A-80A1-BD133E35A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>Auteur:</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>P_AppMobile</t>
+  </si>
+  <si>
+    <t>Finition des maquettes</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1082,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4172,7 +4175,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>3 heures 45 minutes</v>
+        <v>4 heures 30 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4189,11 +4192,11 @@
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4281,15 +4284,23 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="str">
+      <c r="A9" s="74">
         <f>IF(ISBLANK(B9),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B9))</f>
-        <v/>
-      </c>
-      <c r="B9" s="40"/>
+        <v>13</v>
+      </c>
+      <c r="B9" s="40">
+        <v>46106</v>
+      </c>
       <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="28"/>
+      <c r="D9" s="42">
+        <v>45</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="46"/>
       <c r="M9" t="s">
         <v>19</v>
@@ -10803,11 +10814,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10815,7 +10826,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>3 h 45 min</v>
+        <v>4 h 30 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -10914,22 +10925,22 @@
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>3 h 45 min</v>
+        <v>4 h 30 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>4.261363636363636E-2</v>
+        <v>5.113636363636364E-2</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE45E312-BC82-452A-80A1-BD133E35A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1888C1E-449C-423C-BD67-DC2650F2C180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>Implémentation</t>
   </si>
   <si>
-    <t>Nom Prénom</t>
-  </si>
-  <si>
     <t xml:space="preserve">h.      </t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>Finition des maquettes</t>
+  </si>
+  <si>
+    <t>Chabal Damien</t>
   </si>
 </sst>
 </file>
@@ -4147,7 +4147,7 @@
       <c r="D1" s="10"/>
       <c r="E1" s="11"/>
       <c r="F1" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="11"/>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="B2" s="82"/>
       <c r="C2" s="80" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D2" s="80"/>
       <c r="E2" s="80"/>
@@ -4165,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
@@ -4215,7 +4215,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>15</v>
@@ -4248,7 +4248,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" s="44"/>
     </row>
@@ -4270,7 +4270,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="45"/>
       <c r="M8" t="s">
@@ -4299,7 +4299,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="46"/>
       <c r="M9" t="s">
@@ -10713,13 +10713,13 @@
   <sheetData>
     <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E2" s="77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="79">
         <v>88</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L2" s="20"/>
       <c r="M2" s="52"/>
@@ -10732,10 +10732,10 @@
     </row>
     <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="E4" s="77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" s="77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M4" s="48"/>
       <c r="N4" s="24"/>
@@ -10748,7 +10748,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="53" t="s">
@@ -10758,7 +10758,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="59" t="s">
         <v>12</v>
@@ -10767,7 +10767,7 @@
         <v>13</v>
       </c>
       <c r="N5" s="61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -10979,6 +10979,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11191,18 +11203,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11213,6 +11213,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
+    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11231,19 +11244,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
-    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1888C1E-449C-423C-BD67-DC2650F2C180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5341B8D-2D1F-456B-9183-41641AA2451C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="33375" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Auteur:</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Chabal Damien</t>
+  </si>
+  <si>
+    <t>Ajoute du du menu, la page de détail pour un livre</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1085,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>270</c:v>
+                  <c:v>390</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4175,7 +4178,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>4 heures 30 minutes</v>
+        <v>6 heures 30 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4188,7 +4191,7 @@
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
@@ -4196,7 +4199,7 @@
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4313,15 +4316,23 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="73" t="str">
+      <c r="A10" s="73">
         <f>IF(ISBLANK(B10),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B10))</f>
-        <v/>
-      </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37"/>
+        <v>14</v>
+      </c>
+      <c r="B10" s="36">
+        <v>46113</v>
+      </c>
+      <c r="C10" s="37">
+        <v>2</v>
+      </c>
       <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="28"/>
+      <c r="E10" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>33</v>
+      </c>
       <c r="G10" s="45"/>
       <c r="M10" t="s">
         <v>3</v>
@@ -10810,7 +10821,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
@@ -10818,7 +10829,7 @@
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10826,7 +10837,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>4 h 30 min</v>
+        <v>6 h 30 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -10921,7 +10932,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
@@ -10929,18 +10940,18 @@
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>4 h 30 min</v>
+        <v>6 h 30 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>5.113636363636364E-2</v>
+        <v>7.3863636363636367E-2</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5341B8D-2D1F-456B-9183-41641AA2451C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D63359-BD8F-47D2-9B33-B00C42B9F86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33375" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>Auteur:</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>Ajoute du du menu, la page de détail pour un livre</t>
+  </si>
+  <si>
+    <t>Ajoute de l'import d'un livre epub et affichage du livre dans la liste</t>
+  </si>
+  <si>
+    <t>Ajoute de la suppression d'un livre dans la liste</t>
+  </si>
+  <si>
+    <t>Amélioration des maquettes figma</t>
+  </si>
+  <si>
+    <t>Ajoute de l'affichage du contenu des livres</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1097,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>390</c:v>
+                  <c:v>575</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4178,7 +4190,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>6 heures 30 minutes</v>
+        <v>9 heures 35 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4191,15 +4203,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>390</v>
+        <v>575</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4345,15 +4357,25 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="str">
+      <c r="A11" s="74">
         <f>IF(ISBLANK(B11),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B11))</f>
-        <v/>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="28"/>
+        <v>17</v>
+      </c>
+      <c r="B11" s="40">
+        <v>46134</v>
+      </c>
+      <c r="C11" s="41">
+        <v>1</v>
+      </c>
+      <c r="D11" s="42">
+        <v>30</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>34</v>
+      </c>
       <c r="G11" s="46"/>
       <c r="M11" t="s">
         <v>4</v>
@@ -4366,15 +4388,23 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="73" t="str">
+      <c r="A12" s="73">
         <f>IF(ISBLANK(B12),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B12))</f>
-        <v/>
-      </c>
-      <c r="B12" s="36"/>
+        <v>17</v>
+      </c>
+      <c r="B12" s="36">
+        <v>46134</v>
+      </c>
       <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="28"/>
+      <c r="D12" s="38">
+        <v>25</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>35</v>
+      </c>
       <c r="G12" s="45"/>
       <c r="N12">
         <v>5</v>
@@ -4384,15 +4414,23 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="str">
+      <c r="A13" s="74">
         <f>IF(ISBLANK(B13),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="40"/>
+        <v>17</v>
+      </c>
+      <c r="B13" s="40">
+        <v>46134</v>
+      </c>
       <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="28"/>
+      <c r="D13" s="42">
+        <v>10</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>36</v>
+      </c>
       <c r="G13" s="46"/>
       <c r="N13">
         <v>6</v>
@@ -4402,15 +4440,23 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="73" t="str">
+      <c r="A14" s="73">
         <f>IF(ISBLANK(B14),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
+        <v>18</v>
+      </c>
+      <c r="B14" s="36">
+        <v>46141</v>
+      </c>
+      <c r="C14" s="37">
+        <v>1</v>
+      </c>
       <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="28"/>
+      <c r="E14" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>37</v>
+      </c>
       <c r="G14" s="45"/>
       <c r="N14">
         <v>7</v>
@@ -10821,15 +10867,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>575</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10837,7 +10883,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>6 h 30 min</v>
+        <v>9 h 35 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -10932,26 +10978,26 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>390</v>
+        <v>575</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>6 h 30 min</v>
+        <v>9 h 35 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>7.3863636363636367E-2</v>
+        <v>0.10890151515151515</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D63359-BD8F-47D2-9B33-B00C42B9F86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5185BE-3BC2-453A-A8FE-8BA1976EBF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33375" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>Auteur:</t>
   </si>
@@ -142,19 +142,22 @@
     <t>Chabal Damien</t>
   </si>
   <si>
-    <t>Ajoute du du menu, la page de détail pour un livre</t>
-  </si>
-  <si>
-    <t>Ajoute de l'import d'un livre epub et affichage du livre dans la liste</t>
-  </si>
-  <si>
-    <t>Ajoute de la suppression d'un livre dans la liste</t>
-  </si>
-  <si>
     <t>Amélioration des maquettes figma</t>
   </si>
   <si>
-    <t>Ajoute de l'affichage du contenu des livres</t>
+    <t>Ajout de l'affichage du contenu des livres</t>
+  </si>
+  <si>
+    <t>Ajout de la suppression d'un livre dans la liste</t>
+  </si>
+  <si>
+    <t>Ajout de l'import d'un livre epub et affichage du livre dans la liste</t>
+  </si>
+  <si>
+    <t>Ajout du du menu, la page de détail pour un livre</t>
+  </si>
+  <si>
+    <t>Ajout de l'affichage des images du livres et debug de l'affichage avec du texte dans le livre</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1100,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>575</c:v>
+                  <c:v>665</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4190,7 +4193,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>9 heures 35 minutes</v>
+        <v>11 heures 5 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4203,15 +4206,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>575</v>
+        <v>665</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4343,7 +4346,7 @@
         <v>19</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G10" s="45"/>
       <c r="M10" t="s">
@@ -4374,7 +4377,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" s="46"/>
       <c r="M11" t="s">
@@ -4429,7 +4432,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G13" s="46"/>
       <c r="N13">
@@ -4450,12 +4453,14 @@
       <c r="C14" s="37">
         <v>1</v>
       </c>
-      <c r="D14" s="38"/>
+      <c r="D14" s="38">
+        <v>10</v>
+      </c>
       <c r="E14" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G14" s="45"/>
       <c r="N14">
@@ -4466,15 +4471,25 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="74" t="str">
+      <c r="A15" s="74">
         <f>IF(ISBLANK(B15),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B15))</f>
-        <v/>
-      </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="28"/>
+        <v>18</v>
+      </c>
+      <c r="B15" s="40">
+        <v>46141</v>
+      </c>
+      <c r="C15" s="41">
+        <v>1</v>
+      </c>
+      <c r="D15" s="42">
+        <v>20</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>38</v>
+      </c>
       <c r="G15" s="46"/>
       <c r="N15">
         <v>8</v>
@@ -10867,15 +10882,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>575</v>
+        <v>665</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10883,7 +10898,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>9 h 35 min</v>
+        <v>11 h 05 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -10978,26 +10993,26 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>575</v>
+        <v>665</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>9 h 35 min</v>
+        <v>11 h 05 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.10890151515151515</v>
+        <v>0.1259469696969697</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>
@@ -11036,18 +11051,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11260,6 +11263,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11270,19 +11285,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
-    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11301,6 +11303,19 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
+    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5185BE-3BC2-453A-A8FE-8BA1976EBF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEC82AF-6EDE-476E-8E7E-89CD08FF0A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33375" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="30750" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>Auteur:</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>Ajout de l'affichage des images du livres et debug de l'affichage avec du texte dans le livre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification de la lecture pour que se soit page par page </t>
+  </si>
+  <si>
+    <t>Ajoute de la barre de progression dans un livre</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1106,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>665</c:v>
+                  <c:v>785</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4193,7 +4199,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>11 heures 5 minutes</v>
+        <v>13 heures 5 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4206,7 +4212,7 @@
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
@@ -4214,7 +4220,7 @@
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>665</v>
+        <v>785</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4499,30 +4505,46 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="73" t="str">
+      <c r="A16" s="73">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
+        <v>19</v>
+      </c>
+      <c r="B16" s="36">
+        <v>46148</v>
+      </c>
+      <c r="C16" s="37">
+        <v>1</v>
+      </c>
       <c r="D16" s="38"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="28"/>
+      <c r="E16" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>39</v>
+      </c>
       <c r="G16" s="45"/>
       <c r="O16">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="str">
+      <c r="A17" s="74">
         <f>IF(ISBLANK(B17),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
+        <v>19</v>
+      </c>
+      <c r="B17" s="40">
+        <v>46148</v>
+      </c>
+      <c r="C17" s="41">
+        <v>1</v>
+      </c>
       <c r="D17" s="42"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="28"/>
+      <c r="E17" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>40</v>
+      </c>
       <c r="G17" s="46"/>
       <c r="O17">
         <v>45</v>
@@ -10882,7 +10904,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
@@ -10890,7 +10912,7 @@
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>665</v>
+        <v>785</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10898,7 +10920,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>11 h 05 min</v>
+        <v>13 h 05 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -10993,7 +11015,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
@@ -11001,18 +11023,18 @@
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>665</v>
+        <v>785</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>11 h 05 min</v>
+        <v>13 h 05 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.1259469696969697</v>
+        <v>0.14867424242424243</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>
@@ -11051,6 +11073,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11263,18 +11297,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11285,6 +11307,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
+    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11303,19 +11338,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
-    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEC82AF-6EDE-476E-8E7E-89CD08FF0A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9198FD-5D1D-4727-9825-9DBB751FC8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30750" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="6600" yWindow="2670" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
   <si>
     <t>Auteur:</t>
   </si>
@@ -157,13 +157,22 @@
     <t>Ajout du du menu, la page de détail pour un livre</t>
   </si>
   <si>
-    <t>Ajout de l'affichage des images du livres et debug de l'affichage avec du texte dans le livre</t>
-  </si>
-  <si>
     <t xml:space="preserve">Modification de la lecture pour que se soit page par page </t>
   </si>
   <si>
-    <t>Ajoute de la barre de progression dans un livre</t>
+    <t>debug de l'affichage avec du texte dans le livre</t>
+  </si>
+  <si>
+    <t>Ajout de l'affichage des images du livres</t>
+  </si>
+  <si>
+    <t>Ajout de la barre de progression dans un livre</t>
+  </si>
+  <si>
+    <t>Ajout de la mémorisation de la page</t>
+  </si>
+  <si>
+    <t>Ajout de la reprise automatique a la bonne page dans un livre</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1115,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>785</c:v>
+                  <c:v>845</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4199,7 +4208,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>13 heures 5 minutes</v>
+        <v>14 heures 5 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4216,11 +4225,11 @@
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4487,14 +4496,12 @@
       <c r="C15" s="41">
         <v>1</v>
       </c>
-      <c r="D15" s="42">
-        <v>20</v>
-      </c>
+      <c r="D15" s="42"/>
       <c r="E15" s="43" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G15" s="46"/>
       <c r="N15">
@@ -4507,15 +4514,15 @@
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="73">
         <f>IF(ISBLANK(B16),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B16))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="36">
-        <v>46148</v>
-      </c>
-      <c r="C16" s="37">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38"/>
+        <v>46141</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38">
+        <v>20</v>
+      </c>
       <c r="E16" s="39" t="s">
         <v>19</v>
       </c>
@@ -4543,7 +4550,7 @@
         <v>19</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G17" s="46"/>
       <c r="O17">
@@ -4551,45 +4558,69 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="73" t="str">
+      <c r="A18" s="73">
         <f>IF(ISBLANK(B18),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
+        <v>19</v>
+      </c>
+      <c r="B18" s="36">
+        <v>46148</v>
+      </c>
+      <c r="C18" s="37">
+        <v>1</v>
+      </c>
       <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="28"/>
+      <c r="E18" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>41</v>
+      </c>
       <c r="G18" s="45"/>
       <c r="O18">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="74" t="str">
+      <c r="A19" s="74">
         <f>IF(ISBLANK(B19),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="40"/>
+        <v>20</v>
+      </c>
+      <c r="B19" s="40">
+        <v>46155</v>
+      </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="28"/>
+      <c r="D19" s="42">
+        <v>45</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>42</v>
+      </c>
       <c r="G19" s="46"/>
       <c r="O19">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="str">
+      <c r="A20" s="73">
         <f>IF(ISBLANK(B20),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="36"/>
+        <v>20</v>
+      </c>
+      <c r="B20" s="36">
+        <v>46155</v>
+      </c>
       <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="28"/>
+      <c r="D20" s="38">
+        <v>15</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>43</v>
+      </c>
       <c r="G20" s="45"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -10908,11 +10939,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10920,7 +10951,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>13 h 05 min</v>
+        <v>14 h 05 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -11019,22 +11050,22 @@
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>13 h 05 min</v>
+        <v>14 h 05 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.14867424242424243</v>
+        <v>0.16003787878787878</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9198FD-5D1D-4727-9825-9DBB751FC8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BFAB30-948C-4456-BCAB-C75DE56BA61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6600" yWindow="2670" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>Auteur:</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>Ajout de la reprise automatique a la bonne page dans un livre</t>
+  </si>
+  <si>
+    <t>Ajout du tri par date</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1118,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>845</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4208,7 +4211,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>14 heures 5 minutes</v>
+        <v>15 heures 0 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4221,15 +4224,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>845</v>
+        <v>900</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4588,10 +4591,10 @@
       <c r="B19" s="40">
         <v>46155</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42">
-        <v>45</v>
-      </c>
+      <c r="C19" s="41">
+        <v>1</v>
+      </c>
+      <c r="D19" s="42"/>
       <c r="E19" s="43" t="s">
         <v>19</v>
       </c>
@@ -4613,7 +4616,7 @@
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E20" s="39" t="s">
         <v>19</v>
@@ -4624,15 +4627,23 @@
       <c r="G20" s="45"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="74" t="str">
+      <c r="A21" s="74">
         <f>IF(ISBLANK(B21),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="40"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="40">
+        <v>46155</v>
+      </c>
       <c r="C21" s="41"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="28"/>
+      <c r="D21" s="42">
+        <v>30</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>44</v>
+      </c>
       <c r="G21" s="46"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -10935,15 +10946,15 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>845</v>
+        <v>900</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10951,7 +10962,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>14 h 05 min</v>
+        <v>15 h 00 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -11046,26 +11057,26 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>845</v>
+        <v>900</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>14 h 05 min</v>
+        <v>15 h 00 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.16003787878787878</v>
+        <v>0.17045454545454544</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>
@@ -11104,18 +11115,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11328,6 +11327,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11338,19 +11349,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
-    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11369,6 +11367,19 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
+    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BFAB30-948C-4456-BCAB-C75DE56BA61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B5BBE0-5299-409B-931F-F01208E9B5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6600" yWindow="2670" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>Auteur:</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>Ajout du tri par date</t>
+  </si>
+  <si>
+    <t>meilleur affichage</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1121,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900</c:v>
+                  <c:v>930</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4211,7 +4214,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>15 heures 0 minutes</v>
+        <v>15 heures 30 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4228,11 +4231,11 @@
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4647,15 +4650,23 @@
       <c r="G21" s="46"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="73" t="str">
+      <c r="A22" s="73">
         <f>IF(ISBLANK(B22),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="36"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="36">
+        <v>46155</v>
+      </c>
       <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="28"/>
+      <c r="D22" s="38">
+        <v>30</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>45</v>
+      </c>
       <c r="G22" s="45"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -10950,11 +10961,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10962,7 +10973,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>15 h 00 min</v>
+        <v>15 h 30 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -11061,22 +11072,22 @@
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>15 h 00 min</v>
+        <v>15 h 30 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.17045454545454544</v>
+        <v>0.17613636363636365</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>

--- a/Journal-de-Travail_DamienChabal.xlsx
+++ b/Journal-de-Travail_DamienChabal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pv77ngi\Documents\GitHub\P_AppMobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\damie\Documents\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B5BBE0-5299-409B-931F-F01208E9B5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C0C940-B2D2-46D5-96D5-2C3DE7D57112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6600" yWindow="2670" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="2400" yWindow="795" windowWidth="15060" windowHeight="14295" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
   <si>
     <t>Auteur:</t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>meilleur affichage</t>
+  </si>
+  <si>
+    <t>ajout utilisation de l'api pour backend</t>
+  </si>
+  <si>
+    <t>Ajout de la gestion des tages et filtrage</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1127,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>930</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1191,6 +1197,7 @@
     </c:legend>
     <c:plotVisOnly val="0"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1198,7 +1205,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1538,6 +1544,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1545,7 +1552,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2134,6 +2140,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2141,7 +2148,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4214,7 +4220,7 @@
       <c r="B3" s="82"/>
       <c r="C3" s="78" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>15 heures 30 minutes</v>
+        <v>17 heures 30 minutes</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -4227,7 +4233,7 @@
       <c r="B4" s="5"/>
       <c r="C4" s="19">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>660</v>
+        <v>780</v>
       </c>
       <c r="D4" s="19">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
@@ -4235,7 +4241,7 @@
       </c>
       <c r="E4" s="29">
         <f>SUM(C4:D4)</f>
-        <v>930</v>
+        <v>1050</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="6"/>
@@ -4670,27 +4676,43 @@
       <c r="G22" s="45"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="str">
+      <c r="A23" s="74">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="40">
+        <v>46167</v>
+      </c>
+      <c r="C23" s="41">
+        <v>1</v>
+      </c>
       <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="28"/>
+      <c r="E23" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>46</v>
+      </c>
       <c r="G23" s="46"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="str">
+      <c r="A24" s="73">
         <f>IF(ISBLANK(B24),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="36">
+        <v>46167</v>
+      </c>
+      <c r="C24" s="37">
+        <v>1</v>
+      </c>
       <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="28"/>
+      <c r="E24" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>47</v>
+      </c>
       <c r="G24" s="45"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -10957,7 +10979,7 @@
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>660</v>
+        <v>780</v>
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
@@ -10965,7 +10987,7 @@
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>1050</v>
       </c>
       <c r="E7" s="30" t="str">
         <f>'Journal de travail'!M9</f>
@@ -10973,7 +10995,7 @@
       </c>
       <c r="F7" s="55" t="str">
         <f t="shared" ref="F7:F10" si="1">QUOTIENT(SUM(A7:B7),60)&amp;" h "&amp;TEXT(MOD(SUM(A7:B7),60), "00")&amp;" min"</f>
-        <v>15 h 30 min</v>
+        <v>17 h 30 min</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" ref="G7:G9" si="2">SUM(A7:B7)/$C$10</f>
@@ -11068,7 +11090,7 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>SUM(A6:A9)</f>
-        <v>660</v>
+        <v>780</v>
       </c>
       <c r="B10">
         <f>SUM(B6:B9)</f>
@@ -11076,18 +11098,18 @@
       </c>
       <c r="C10">
         <f>SUM(A10:B10)</f>
-        <v>930</v>
+        <v>1050</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
-        <v>15 h 30 min</v>
+        <v>17 h 30 min</v>
       </c>
       <c r="G10" s="57">
         <f>C10/C11</f>
-        <v>0.17613636363636365</v>
+        <v>0.19886363636363635</v>
       </c>
       <c r="L10" s="67" t="s">
         <v>18</v>
@@ -11126,6 +11148,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C9F2488912074FB587B9AD9ADAE5BB" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="020ab319e6f8d23aec07c29d6516d4ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xmlns:ns3="eefa3612-053e-497a-ae76-8a76877f5e22" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e15d3f914bf2a775f9387e5284d9197" ns2:_="" ns3:_="">
     <xsd:import namespace="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
@@ -11338,42 +11381,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eefa3612-053e-497a-ae76-8a76877f5e22" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <img xmlns="b5cf4370-ac38-4b9e-9836-ef6f5df64f24" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
-    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11392,9 +11403,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6394C10-4386-493D-A99B-15992834CB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5cf4370-ac38-4b9e-9836-ef6f5df64f24"/>
+    <ds:schemaRef ds:uri="eefa3612-053e-497a-ae76-8a76877f5e22"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>